--- a/excel-files/MUNTINLUPA/TUNASAN NATIONAL HIGH SCHOOL.xlsx
+++ b/excel-files/MUNTINLUPA/TUNASAN NATIONAL HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="272" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68369AFB-17C3-41D8-B9AF-D160358E6CD4}"/>
+  <xr:revisionPtr revIDLastSave="308" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E673243D-F2BC-4F8E-944F-5806ECDEEFD7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="85">
   <si>
     <t>Grade Level</t>
   </si>
@@ -468,7 +468,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -560,30 +560,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -597,7 +573,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -671,22 +647,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2972,8 +2939,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H97" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
-  <autoFilter ref="A1:H97" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H49" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+  <autoFilter ref="A1:H49" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
     <tableColumn id="2" xr3:uid="{56826189-DC15-4CA2-B5A0-8F4CEC09DDAB}" name="SUBJECTS"/>
@@ -2989,8 +2956,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA68" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
-  <autoFilter ref="A2:AA68" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA50" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+  <autoFilter ref="A2:AA50" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
     <tableColumn id="2" xr3:uid="{C6CCCB1C-6639-4C28-A4BA-B187B2F73B59}" name="SUBJECTS" dataDxfId="55"/>
@@ -3045,8 +3012,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA77" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
-  <autoFilter ref="A2:AA77" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA58" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+  <autoFilter ref="A2:AA58" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
     <tableColumn id="2" xr3:uid="{73AEA048-228E-40E8-B07A-3A7C30BA0DC7}" name="SUBJECTS" dataDxfId="25"/>
@@ -3417,7 +3384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -3455,21 +3422,39 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="27" customHeight="1">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" spans="1:8" ht="27" customHeight="1">
+      <c r="A2" s="8">
+        <v>7</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="8">
+        <v>1499</v>
+      </c>
+      <c r="D2" s="8">
+        <v>1739</v>
+      </c>
+      <c r="E2" s="8">
+        <v>2025</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2">
+        <f t="shared" ref="G2:G10" si="0">IF((C2-D2)&lt;0,0,C2-D2)</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <f t="shared" ref="H2:H10" si="1">IF((D2-C2)&lt;0,0,D2-C2)</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="21" customHeight="1">
       <c r="A3" s="8">
         <v>7</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="8">
         <v>1499</v>
@@ -3478,26 +3463,26 @@
         <v>1739</v>
       </c>
       <c r="E3" s="8">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G11" si="0">IF((C3-D3)&lt;0,0,C3-D3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <f t="shared" ref="H3:H11" si="1">IF((D3-C3)&lt;0,0,D3-C3)</f>
+        <f t="shared" si="1"/>
         <v>240</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1">
+    <row r="4" spans="1:8" ht="25.5" customHeight="1">
       <c r="A4" s="8">
         <v>7</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="8">
         <v>1499</v>
@@ -3506,7 +3491,7 @@
         <v>1739</v>
       </c>
       <c r="E4" s="8">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>9</v>
@@ -3520,12 +3505,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1">
+    <row r="5" spans="1:8" ht="19.5">
       <c r="A5" s="8">
         <v>7</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="8">
         <v>1499</v>
@@ -3534,7 +3519,7 @@
         <v>1739</v>
       </c>
       <c r="E5" s="8">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>9</v>
@@ -3548,12 +3533,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.5">
+    <row r="6" spans="1:8" ht="38.25">
       <c r="A6" s="8">
         <v>7</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="8">
         <v>1499</v>
@@ -3562,7 +3547,7 @@
         <v>1739</v>
       </c>
       <c r="E6" s="8">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>9</v>
@@ -3576,12 +3561,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="38.25">
+    <row r="7" spans="1:8" ht="39.75" customHeight="1">
       <c r="A7" s="8">
         <v>7</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="8">
         <v>1499</v>
@@ -3590,7 +3575,7 @@
         <v>1739</v>
       </c>
       <c r="E7" s="8">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>9</v>
@@ -3604,12 +3589,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="39.75" customHeight="1">
+    <row r="8" spans="1:8" ht="29.25" customHeight="1">
       <c r="A8" s="8">
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="8">
         <v>1499</v>
@@ -3618,7 +3603,7 @@
         <v>1739</v>
       </c>
       <c r="E8" s="8">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>9</v>
@@ -3632,12 +3617,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" customHeight="1">
+    <row r="9" spans="1:8" ht="28.5" customHeight="1">
       <c r="A9" s="8">
         <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="8">
         <v>1499</v>
@@ -3660,12 +3645,12 @@
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1">
+    <row r="10" spans="1:8" ht="24" customHeight="1">
       <c r="A10" s="8">
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="8">
         <v>1499</v>
@@ -3688,50 +3673,46 @@
         <v>240</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1">
-      <c r="A11" s="8">
-        <v>7</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="8">
-        <v>1499</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1739</v>
-      </c>
-      <c r="E11" s="8">
-        <v>2025</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="3">
-        <f t="shared" si="1"/>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" ht="19.5">
+    <row r="11" spans="1:8" ht="15">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" ht="19.5">
+      <c r="A12" s="8">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="8">
+        <v>1450</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="2">
+        <f t="shared" ref="G12:G20" si="2">IF((C12-D12)&lt;0,0,C12-D12)</f>
+        <v>1450</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" ref="H12:H20" si="3">IF((D12-C12)&lt;0,0,D12-C12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="49.5" customHeight="1">
       <c r="A13" s="8">
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C13" s="8">
         <v>1450</v>
@@ -3742,44 +3723,48 @@
       <c r="E13" s="8"/>
       <c r="F13" s="10"/>
       <c r="G13" s="2">
-        <f t="shared" ref="G13:G21" si="2">IF((C13-D13)&lt;0,0,C13-D13)</f>
+        <f t="shared" si="2"/>
         <v>1450</v>
       </c>
       <c r="H13" s="3">
-        <f t="shared" ref="H13:H21" si="3">IF((D13-C13)&lt;0,0,D13-C13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="49.5" customHeight="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="29.25" customHeight="1">
       <c r="A14" s="8">
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="8">
         <v>1450</v>
       </c>
       <c r="D14" s="8">
-        <v>0</v>
-      </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="10"/>
+        <v>1282</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2025</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="G14" s="2">
         <f t="shared" si="2"/>
-        <v>1450</v>
+        <v>168</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" customHeight="1">
+    <row r="15" spans="1:8" ht="27" customHeight="1">
       <c r="A15" s="8">
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="8">
         <v>1450</v>
@@ -3802,80 +3787,76 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" customHeight="1">
+    <row r="16" spans="1:8" ht="23.25" customHeight="1">
       <c r="A16" s="8">
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C16" s="8">
         <v>1450</v>
       </c>
       <c r="D16" s="8">
-        <v>1282</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2025</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="10"/>
       <c r="G16" s="2">
         <f t="shared" si="2"/>
-        <v>168</v>
+        <v>1450</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" customHeight="1">
+    <row r="17" spans="1:8" ht="21" customHeight="1">
       <c r="A17" s="8">
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C17" s="8">
         <v>1450</v>
       </c>
       <c r="D17" s="8">
-        <v>0</v>
-      </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="10"/>
+        <v>1282</v>
+      </c>
+      <c r="E17" s="8">
+        <v>2026</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="G17" s="2">
         <f t="shared" si="2"/>
-        <v>1450</v>
+        <v>168</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1">
+    <row r="18" spans="1:8" ht="19.5">
       <c r="A18" s="8">
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="8">
         <v>1450</v>
       </c>
       <c r="D18" s="8">
-        <v>1282</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2026</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="10"/>
       <c r="G18" s="2">
         <f t="shared" si="2"/>
-        <v>168</v>
+        <v>1450</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="3"/>
@@ -3887,7 +3868,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" s="8">
         <v>1450</v>
@@ -3906,12 +3887,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="19.5">
+    <row r="20" spans="1:8" ht="28.5" customHeight="1">
       <c r="A20" s="8">
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" s="8">
         <v>1450</v>
@@ -3930,46 +3911,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="28.5" customHeight="1">
-      <c r="A21" s="8">
+    <row r="21" spans="1:8" ht="24" customHeight="1">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="19.5">
+      <c r="A22" s="8">
+        <v>9</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="8">
-        <v>1450</v>
-      </c>
-      <c r="D21" s="8">
-        <v>0</v>
-      </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="2">
-        <f t="shared" si="2"/>
-        <v>1450</v>
-      </c>
-      <c r="H21" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="1:8" ht="19.5">
+      <c r="C22" s="8">
+        <v>1128</v>
+      </c>
+      <c r="D22" s="8">
+        <v>0</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="2">
+        <f t="shared" ref="G22:G30" si="4">IF((C22-D22)&lt;0,0,C22-D22)</f>
+        <v>1128</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" ref="H22:H30" si="5">IF((D22-C22)&lt;0,0,D22-C22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="27" customHeight="1">
       <c r="A23" s="8">
         <v>9</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C23" s="8">
         <v>1128</v>
@@ -3980,20 +3961,20 @@
       <c r="E23" s="8"/>
       <c r="F23" s="10"/>
       <c r="G23" s="2">
-        <f t="shared" ref="G23:G31" si="4">IF((C23-D23)&lt;0,0,C23-D23)</f>
+        <f t="shared" si="4"/>
         <v>1128</v>
       </c>
       <c r="H23" s="3">
-        <f t="shared" ref="H23:H31" si="5">IF((D23-C23)&lt;0,0,D23-C23)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="27" customHeight="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="33.75" customHeight="1">
       <c r="A24" s="8">
         <v>9</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" s="8">
         <v>1128</v>
@@ -4017,7 +3998,7 @@
         <v>9</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25" s="8">
         <v>1128</v>
@@ -4041,7 +4022,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C26" s="8">
         <v>1128</v>
@@ -4060,12 +4041,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="33.75" customHeight="1">
+    <row r="27" spans="1:8" ht="27.75" customHeight="1">
       <c r="A27" s="8">
         <v>9</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C27" s="8">
         <v>1128</v>
@@ -4089,7 +4070,7 @@
         <v>9</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" s="8">
         <v>1128</v>
@@ -4113,7 +4094,7 @@
         <v>9</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="8">
         <v>1128</v>
@@ -4137,7 +4118,7 @@
         <v>9</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C30" s="8">
         <v>1128</v>
@@ -4157,45 +4138,45 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A31" s="8">
-        <v>9</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" s="8">
-        <v>1128</v>
-      </c>
-      <c r="D31" s="8">
-        <v>0</v>
-      </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="2">
-        <f t="shared" si="4"/>
-        <v>1128</v>
-      </c>
-      <c r="H31" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="A31" s="5"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
+      <c r="A32" s="8">
+        <v>10</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="8">
+        <v>1222</v>
+      </c>
+      <c r="D32" s="8">
+        <v>0</v>
+      </c>
+      <c r="E32" s="8"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="2">
+        <f t="shared" ref="G32:G40" si="6">IF((C32-D32)&lt;0,0,C32-D32)</f>
+        <v>1222</v>
+      </c>
+      <c r="H32" s="3">
+        <f t="shared" ref="H32:H40" si="7">IF((D32-C32)&lt;0,0,D32-C32)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="1:8" ht="27.75" customHeight="1">
       <c r="A33" s="8">
         <v>10</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C33" s="8">
         <v>1222</v>
@@ -4206,20 +4187,20 @@
       <c r="E33" s="8"/>
       <c r="F33" s="10"/>
       <c r="G33" s="2">
-        <f t="shared" ref="G33:G41" si="6">IF((C33-D33)&lt;0,0,C33-D33)</f>
+        <f t="shared" si="6"/>
         <v>1222</v>
       </c>
       <c r="H33" s="3">
-        <f t="shared" ref="H33:H41" si="7">IF((D33-C33)&lt;0,0,D33-C33)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="27.75" customHeight="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="39" customHeight="1">
       <c r="A34" s="8">
         <v>10</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="8">
         <v>1222</v>
@@ -4238,12 +4219,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" customHeight="1">
+    <row r="35" spans="1:8" ht="27.75" customHeight="1">
       <c r="A35" s="8">
         <v>10</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C35" s="8">
         <v>1222</v>
@@ -4267,7 +4248,7 @@
         <v>10</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C36" s="8">
         <v>1222</v>
@@ -4291,7 +4272,7 @@
         <v>10</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C37" s="8">
         <v>1222</v>
@@ -4315,7 +4296,7 @@
         <v>10</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" s="8">
         <v>1222</v>
@@ -4339,7 +4320,7 @@
         <v>10</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C39" s="8">
         <v>1222</v>
@@ -4363,7 +4344,7 @@
         <v>10</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C40" s="8">
         <v>1222</v>
@@ -4383,97 +4364,101 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A41" s="8">
-        <v>10</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C41" s="8">
-        <v>1222</v>
-      </c>
-      <c r="D41" s="8">
-        <v>0</v>
-      </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="2">
-        <f t="shared" si="6"/>
-        <v>1222</v>
-      </c>
-      <c r="H41" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-    </row>
-    <row r="43" spans="1:8" ht="33" customHeight="1">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" spans="1:8" ht="33" customHeight="1">
+      <c r="A42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="1">
+        <v>822</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1157</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="2">
+        <f t="shared" ref="G42:G49" si="8">IF((C42-D42)&lt;0,0,C42-D42)</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <f t="shared" ref="H42:H49" si="9">IF((D42-C42)&lt;0,0,D42-C42)</f>
+        <v>335</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="33.75" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C43" s="1">
         <v>822</v>
       </c>
       <c r="D43" s="1">
-        <v>1157</v>
-      </c>
-      <c r="E43" s="1">
-        <v>2024</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="4"/>
       <c r="G43" s="2">
-        <f t="shared" ref="G43:G50" si="8">IF((C43-D43)&lt;0,0,C43-D43)</f>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>822</v>
       </c>
       <c r="H43" s="3">
-        <f t="shared" ref="H43:H50" si="9">IF((D43-C43)&lt;0,0,D43-C43)</f>
-        <v>335</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="33.75" customHeight="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="36.75" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C44" s="1">
         <v>822</v>
       </c>
       <c r="D44" s="1">
-        <v>0</v>
-      </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="4"/>
+        <v>1157</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="G44" s="2">
         <f t="shared" si="8"/>
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="H44" s="3">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="36.75" customHeight="1">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="27.75" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C45" s="1">
         <v>822</v>
@@ -4496,56 +4481,56 @@
         <v>335</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" customHeight="1">
+    <row r="46" spans="1:8" ht="40.5" customHeight="1">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C46" s="1">
         <v>822</v>
       </c>
       <c r="D46" s="1">
-        <v>1157</v>
-      </c>
-      <c r="E46" s="1">
-        <v>2025</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="4"/>
       <c r="G46" s="2">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>822</v>
       </c>
       <c r="H46" s="3">
         <f t="shared" si="9"/>
-        <v>335</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="40.5" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="27.75" customHeight="1">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C47" s="1">
         <v>822</v>
       </c>
       <c r="D47" s="1">
-        <v>0</v>
-      </c>
-      <c r="E47" s="1"/>
-      <c r="F47" s="4"/>
+        <v>1157</v>
+      </c>
+      <c r="E47" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="G47" s="2">
         <f t="shared" si="8"/>
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="H47" s="3">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>335</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="27.75" customHeight="1">
@@ -4553,7 +4538,7 @@
         <v>19</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C48" s="1">
         <v>822</v>
@@ -4581,7 +4566,7 @@
         <v>19</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C49" s="1">
         <v>822</v>
@@ -4604,39 +4589,12 @@
         <v>335</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A50" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C50" s="1">
-        <v>822</v>
-      </c>
-      <c r="D50" s="1">
-        <v>1157</v>
-      </c>
-      <c r="E50" s="1">
-        <v>2025</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G50" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="3">
-        <f t="shared" si="9"/>
-        <v>335</v>
-      </c>
-    </row>
+    <row r="50" spans="1:8" ht="27.75" customHeight="1"/>
     <row r="51" spans="1:8" ht="27.75" customHeight="1"/>
     <row r="52" spans="1:8" ht="27.75" customHeight="1"/>
     <row r="53" spans="1:8" ht="27.75" customHeight="1"/>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1"/>
-    <row r="55" spans="1:8" ht="39" customHeight="1"/>
+    <row r="54" spans="1:8" ht="39" customHeight="1"/>
+    <row r="55" spans="1:8" ht="27.75" customHeight="1"/>
     <row r="56" spans="1:8" ht="27.75" customHeight="1"/>
     <row r="57" spans="1:8" ht="27.75" customHeight="1"/>
     <row r="58" spans="1:8" ht="27.75" customHeight="1"/>
@@ -4671,34 +4629,33 @@
     <row r="87" ht="27.75" customHeight="1"/>
     <row r="88" ht="27.75" customHeight="1"/>
     <row r="89" ht="27.75" customHeight="1"/>
-    <row r="90" ht="27.75" customHeight="1"/>
-    <row r="91" ht="39.75" customHeight="1"/>
+    <row r="90" ht="39.75" customHeight="1"/>
+    <row r="91" ht="27.75" customHeight="1"/>
     <row r="92" ht="27.75" customHeight="1"/>
     <row r="93" ht="27.75" customHeight="1"/>
-    <row r="94" ht="27.75" customHeight="1"/>
-    <row r="95" ht="40.5" customHeight="1"/>
-    <row r="96" ht="38.25" customHeight="1"/>
-    <row r="97" ht="27.75" customHeight="1"/>
-    <row r="98" ht="47.25" customHeight="1"/>
+    <row r="94" ht="40.5" customHeight="1"/>
+    <row r="95" ht="38.25" customHeight="1"/>
+    <row r="96" ht="27.75" customHeight="1"/>
+    <row r="97" ht="47.25" customHeight="1"/>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C1:E2 C12:E12 C22:E42 C43:D50 C3:D11 C13:D21" name="Textbooks"/>
-    <protectedRange sqref="F1:F2 F12 F22:F42" name="SOURCE"/>
-    <protectedRange sqref="E3:E11" name="Textbooks_3"/>
-    <protectedRange sqref="F3:F11" name="SOURCE_3"/>
-    <protectedRange sqref="E13:E14 E17:E21" name="Textbooks_1"/>
-    <protectedRange sqref="F13:F14 F17:F21" name="SOURCE_1"/>
-    <protectedRange sqref="E15:E16" name="Textbooks_4"/>
-    <protectedRange sqref="F15:F16" name="SOURCE_4"/>
-    <protectedRange sqref="E43:E50" name="Textbooks_2"/>
-    <protectedRange sqref="F43:F50" name="SOURCE_2"/>
+    <protectedRange sqref="C12:D20 C11:E11 C21:E41 C42:D49 C2:D10 C1:E1" name="Textbooks"/>
+    <protectedRange sqref="F21:F41 F11 F1" name="SOURCE"/>
+    <protectedRange sqref="E2:E10" name="Textbooks_3"/>
+    <protectedRange sqref="F2:F10" name="SOURCE_3"/>
+    <protectedRange sqref="E12:E13 E16:E20" name="Textbooks_1"/>
+    <protectedRange sqref="F12:F13 F16:F20" name="SOURCE_1"/>
+    <protectedRange sqref="E14:E15" name="Textbooks_4"/>
+    <protectedRange sqref="F14:F15" name="SOURCE_4"/>
+    <protectedRange sqref="E42:E49" name="Textbooks_2"/>
+    <protectedRange sqref="F42:F49" name="SOURCE_2"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E43:E50 E3:E11 E13:E21 E23:E31 E33:E41" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42:E49 E2:E10 E12:E20 E22:E30 E32:E40" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F21 F43:F50 F23:F31 F33:F41 F3:F11" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12:F20 F42:F49 F22:F30 F32:F40 F2:F10" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4711,7 +4668,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA127"/>
+  <dimension ref="A1:AA126"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -4741,38 +4698,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="26" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="36" t="s">
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="37" t="s">
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="38" t="s">
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
-      <c r="AA1" s="38"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="13" t="s">
@@ -4811,10 +4768,10 @@
       <c r="L2" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="N2" s="33" t="s">
+      <c r="N2" s="30" t="s">
         <v>42</v>
       </c>
       <c r="O2" s="20" t="s">
@@ -4847,51 +4804,101 @@
       <c r="X2" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="Y2" s="34" t="s">
+      <c r="Y2" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="Z2" s="34" t="s">
+      <c r="Z2" s="31" t="s">
         <v>54</v>
       </c>
       <c r="AA2" s="24" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="11"/>
-      <c r="AA3" s="11"/>
-    </row>
-    <row r="4" spans="1:27" s="5" customFormat="1" ht="19.5">
+    <row r="3" spans="1:27" s="5" customFormat="1" ht="19.5">
+      <c r="A3" s="8">
+        <v>7</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="8">
+        <v>1499</v>
+      </c>
+      <c r="D3" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11992</v>
+      </c>
+      <c r="E3" s="10">
+        <v>0</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f t="shared" ref="H3:H17" si="0">IF((D3-E3)&lt;0,0,(D3-E3))</f>
+        <v>11992</v>
+      </c>
+      <c r="I3" s="10">
+        <f t="shared" ref="I3:I17" si="1">IF((E3-D3)&lt;0,0,(E3-D3))</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11992</v>
+      </c>
+      <c r="K3" s="10">
+        <v>0</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10">
+        <f t="shared" ref="N3:N9" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
+        <v>11992</v>
+      </c>
+      <c r="O3" s="10">
+        <f t="shared" ref="O3:O9" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11992</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10">
+        <f t="shared" ref="T3:T9" si="4">IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
+        <v>11992</v>
+      </c>
+      <c r="U3" s="10">
+        <f t="shared" ref="U3:U9" si="5">IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
+        <v>0</v>
+      </c>
+      <c r="V3" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11992</v>
+      </c>
+      <c r="W3" s="10">
+        <v>0</v>
+      </c>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10">
+        <f t="shared" ref="Z3:Z9" si="6">IF((V3-W3)&lt;0,0,(V3-W3))</f>
+        <v>11992</v>
+      </c>
+      <c r="AA3" s="10">
+        <f t="shared" ref="AA3:AA9" si="7">IF((W3-V3)&lt;0,0,(W3-V3))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="8">
         <v>7</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" s="8">
         <v>1499</v>
@@ -4906,11 +4913,11 @@
       <c r="F4" s="8"/>
       <c r="G4" s="10"/>
       <c r="H4" s="10">
-        <f t="shared" ref="H4:H18" si="0">IF((D4-E4)&lt;0,0,(D4-E4))</f>
+        <f t="shared" si="0"/>
         <v>11992</v>
       </c>
       <c r="I4" s="10">
-        <f t="shared" ref="I4:I18" si="1">IF((E4-D4)&lt;0,0,(E4-D4))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J4" s="10">
@@ -4923,11 +4930,11 @@
       <c r="L4" s="8"/>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
-        <f t="shared" ref="N4:N10" si="2">IF((J4-K4)&lt;0,0,(J4-K4))</f>
+        <f t="shared" si="2"/>
         <v>11992</v>
       </c>
       <c r="O4" s="10">
-        <f t="shared" ref="O4:O10" si="3">IF((K4-J4)&lt;0,0,(K4-J4))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P4" s="10">
@@ -4940,11 +4947,11 @@
       <c r="R4" s="8"/>
       <c r="S4" s="10"/>
       <c r="T4" s="10">
-        <f t="shared" ref="T4:T10" si="4">IF((P4-Q4)&lt;0,0,(P4-Q4))</f>
+        <f t="shared" si="4"/>
         <v>11992</v>
       </c>
       <c r="U4" s="10">
-        <f t="shared" ref="U4:U10" si="5">IF((Q4-P4)&lt;0,0,(Q4-P4))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V4" s="10">
@@ -4957,11 +4964,11 @@
       <c r="X4" s="8"/>
       <c r="Y4" s="10"/>
       <c r="Z4" s="10">
-        <f t="shared" ref="Z4:Z10" si="6">IF((V4-W4)&lt;0,0,(V4-W4))</f>
+        <f t="shared" si="6"/>
         <v>11992</v>
       </c>
       <c r="AA4" s="10">
-        <f t="shared" ref="AA4:AA10" si="7">IF((W4-V4)&lt;0,0,(W4-V4))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -4970,7 +4977,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="8">
         <v>1499</v>
@@ -5049,7 +5056,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="8">
         <v>1499</v>
@@ -5123,12 +5130,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="38.25">
       <c r="A7" s="8">
         <v>7</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="8">
         <v>1499</v>
@@ -5202,12 +5209,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="38.25">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="8">
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="8">
         <v>1499</v>
@@ -5286,7 +5293,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" s="8">
         <v>1499</v>
@@ -5365,7 +5372,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="8">
         <v>1499</v>
@@ -5397,11 +5404,11 @@
       <c r="L10" s="8"/>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="N10:N50" si="8">IF((J10-K10)&lt;0,0,(J10-K10))</f>
         <v>11992</v>
       </c>
       <c r="O10" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="O10:O50" si="9">IF((K10-J10)&lt;0,0,(K10-J10))</f>
         <v>0</v>
       </c>
       <c r="P10" s="10">
@@ -5414,11 +5421,11 @@
       <c r="R10" s="8"/>
       <c r="S10" s="10"/>
       <c r="T10" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="T10:T50" si="10">IF((P10-Q10)&lt;0,0,(P10-Q10))</f>
         <v>11992</v>
       </c>
       <c r="U10" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="U10:U50" si="11">IF((Q10-P10)&lt;0,0,(Q10-P10))</f>
         <v>0</v>
       </c>
       <c r="V10" s="10">
@@ -5431,11 +5438,11 @@
       <c r="X10" s="8"/>
       <c r="Y10" s="10"/>
       <c r="Z10" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="Z10:Z50" si="12">IF((V10-W10)&lt;0,0,(V10-W10))</f>
         <v>11992</v>
       </c>
       <c r="AA10" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="AA10:AA50" si="13">IF((W10-V10)&lt;0,0,(W10-V10))</f>
         <v>0</v>
       </c>
     </row>
@@ -5444,7 +5451,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="8">
         <v>1499</v>
@@ -5476,11 +5483,11 @@
       <c r="L11" s="8"/>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
-        <f t="shared" ref="N11:N67" si="8">IF((J11-K11)&lt;0,0,(J11-K11))</f>
+        <f t="shared" si="8"/>
         <v>11992</v>
       </c>
       <c r="O11" s="10">
-        <f t="shared" ref="O11:O67" si="9">IF((K11-J11)&lt;0,0,(K11-J11))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P11" s="10">
@@ -5493,11 +5500,11 @@
       <c r="R11" s="8"/>
       <c r="S11" s="10"/>
       <c r="T11" s="10">
-        <f t="shared" ref="T11:T68" si="10">IF((P11-Q11)&lt;0,0,(P11-Q11))</f>
+        <f t="shared" si="10"/>
         <v>11992</v>
       </c>
       <c r="U11" s="10">
-        <f t="shared" ref="U11:U68" si="11">IF((Q11-P11)&lt;0,0,(Q11-P11))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V11" s="10">
@@ -5510,113 +5517,117 @@
       <c r="X11" s="8"/>
       <c r="Y11" s="10"/>
       <c r="Z11" s="10">
-        <f t="shared" ref="Z11:Z68" si="12">IF((V11-W11)&lt;0,0,(V11-W11))</f>
+        <f t="shared" si="12"/>
         <v>11992</v>
       </c>
       <c r="AA11" s="10">
-        <f t="shared" ref="AA11:AA68" si="13">IF((W11-V11)&lt;0,0,(W11-V11))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="19.5">
-      <c r="A12" s="8">
-        <v>7</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="8">
-        <v>1499</v>
-      </c>
-      <c r="D12" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11992</v>
-      </c>
-      <c r="E12" s="10">
-        <v>0</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" s="5" customFormat="1" ht="19.5">
+      <c r="J12" s="11"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="11"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="11"/>
+      <c r="AA12" s="11"/>
+    </row>
+    <row r="13" spans="1:27" ht="19.5">
+      <c r="A13" s="8">
+        <v>8</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1450</v>
+      </c>
+      <c r="D13" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11600</v>
+      </c>
+      <c r="E13" s="10">
+        <v>163</v>
+      </c>
+      <c r="F13" s="8">
+        <v>2025</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="10">
         <f t="shared" si="0"/>
-        <v>11992</v>
-      </c>
-      <c r="I12" s="10">
+        <v>11437</v>
+      </c>
+      <c r="I13" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11992</v>
-      </c>
-      <c r="K12" s="10">
-        <v>0</v>
-      </c>
-      <c r="L12" s="8"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10">
+      <c r="J13" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11600</v>
+      </c>
+      <c r="K13" s="10">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10">
         <f t="shared" si="8"/>
-        <v>11992</v>
-      </c>
-      <c r="O12" s="10">
+        <v>11600</v>
+      </c>
+      <c r="O13" s="10">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="P12" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11992</v>
-      </c>
-      <c r="Q12" s="10">
-        <v>0</v>
-      </c>
-      <c r="R12" s="8"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10">
+      <c r="P13" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11600</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10">
         <f t="shared" si="10"/>
-        <v>11992</v>
-      </c>
-      <c r="U12" s="10">
+        <v>11600</v>
+      </c>
+      <c r="U13" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="V12" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11992</v>
-      </c>
-      <c r="W12" s="10">
-        <v>0</v>
-      </c>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10">
+      <c r="V13" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11600</v>
+      </c>
+      <c r="W13" s="10">
+        <v>0</v>
+      </c>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10">
         <f t="shared" si="12"/>
-        <v>11992</v>
-      </c>
-      <c r="AA12" s="10">
+        <v>11600</v>
+      </c>
+      <c r="AA13" s="10">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" s="5" customFormat="1" ht="19.5">
-      <c r="J13" s="11"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="11"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="11"/>
-      <c r="AA13" s="11"/>
     </row>
     <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="8">
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C14" s="8">
         <v>1450</v>
@@ -5699,7 +5710,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="8">
         <v>1450</v>
@@ -5782,7 +5793,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" s="8">
         <v>1450</v>
@@ -5865,7 +5876,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C17" s="8">
         <v>1450</v>
@@ -5948,7 +5959,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C18" s="8">
         <v>1450</v>
@@ -5967,11 +5978,11 @@
         <v>56</v>
       </c>
       <c r="H18" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H18:H50" si="14">IF((D18-E18)&lt;0,0,(D18-E18))</f>
         <v>11437</v>
       </c>
       <c r="I18" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I18:I50" si="15">IF((E18-D18)&lt;0,0,(E18-D18))</f>
         <v>0</v>
       </c>
       <c r="J18" s="10">
@@ -6031,7 +6042,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" s="8">
         <v>1450</v>
@@ -6050,11 +6061,11 @@
         <v>56</v>
       </c>
       <c r="H19" s="10">
-        <f t="shared" ref="H19:H68" si="14">IF((D19-E19)&lt;0,0,(D19-E19))</f>
+        <f t="shared" si="14"/>
         <v>11437</v>
       </c>
       <c r="I19" s="10">
-        <f t="shared" ref="I19:I68" si="15">IF((E19-D19)&lt;0,0,(E19-D19))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J19" s="10">
@@ -6114,7 +6125,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="8">
         <v>1450</v>
@@ -6192,12 +6203,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.5">
+    <row r="21" spans="1:27" s="5" customFormat="1" ht="19.5">
       <c r="A21" s="8">
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" s="8">
         <v>1450</v>
@@ -6275,124 +6286,120 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="5" customFormat="1" ht="19.5">
-      <c r="A22" s="8">
+    <row r="22" spans="1:27" ht="19.5">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="11"/>
+      <c r="AA22" s="11"/>
+    </row>
+    <row r="23" spans="1:27" ht="19.5">
+      <c r="A23" s="8">
+        <v>9</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="8">
-        <v>1450</v>
-      </c>
-      <c r="D22" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11600</v>
-      </c>
-      <c r="E22" s="10">
-        <v>163</v>
-      </c>
-      <c r="F22" s="8">
-        <v>2025</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H22" s="10">
+      <c r="C23" s="8">
+        <v>1128</v>
+      </c>
+      <c r="D23" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9024</v>
+      </c>
+      <c r="E23" s="10">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10">
         <f t="shared" si="14"/>
-        <v>11437</v>
-      </c>
-      <c r="I22" s="10">
+        <v>9024</v>
+      </c>
+      <c r="I23" s="10">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J22" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11600</v>
-      </c>
-      <c r="K22" s="10">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10">
+      <c r="J23" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9024</v>
+      </c>
+      <c r="K23" s="10">
+        <v>0</v>
+      </c>
+      <c r="L23" s="8"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10">
         <f t="shared" si="8"/>
-        <v>11600</v>
-      </c>
-      <c r="O22" s="10">
+        <v>9024</v>
+      </c>
+      <c r="O23" s="10">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="P22" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11600</v>
-      </c>
-      <c r="Q22" s="10">
-        <v>0</v>
-      </c>
-      <c r="R22" s="8"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="10">
+      <c r="P23" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9024</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10">
         <f t="shared" si="10"/>
-        <v>11600</v>
-      </c>
-      <c r="U22" s="10">
+        <v>9024</v>
+      </c>
+      <c r="U23" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="V22" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11600</v>
-      </c>
-      <c r="W22" s="10">
-        <v>0</v>
-      </c>
-      <c r="X22" s="8"/>
-      <c r="Y22" s="10"/>
-      <c r="Z22" s="10">
+      <c r="V23" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9024</v>
+      </c>
+      <c r="W23" s="10">
+        <v>0</v>
+      </c>
+      <c r="X23" s="8"/>
+      <c r="Y23" s="10"/>
+      <c r="Z23" s="10">
         <f t="shared" si="12"/>
-        <v>11600</v>
-      </c>
-      <c r="AA22" s="10">
+        <v>9024</v>
+      </c>
+      <c r="AA23" s="10">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:27" ht="19.5">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="11"/>
-      <c r="U23" s="11"/>
-      <c r="V23" s="11"/>
-      <c r="W23" s="5"/>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="4"/>
-      <c r="Z23" s="11"/>
-      <c r="AA23" s="11"/>
     </row>
     <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="8">
         <v>9</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C24" s="8">
         <v>1128</v>
@@ -6471,7 +6478,7 @@
         <v>9</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="8">
         <v>1128</v>
@@ -6550,7 +6557,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C26" s="8">
         <v>1128</v>
@@ -6629,7 +6636,7 @@
         <v>9</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C27" s="8">
         <v>1128</v>
@@ -6708,7 +6715,7 @@
         <v>9</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C28" s="8">
         <v>1128</v>
@@ -6787,7 +6794,7 @@
         <v>9</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="8">
         <v>1128</v>
@@ -6866,7 +6873,7 @@
         <v>9</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C30" s="8">
         <v>1128</v>
@@ -6940,12 +6947,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.5">
+    <row r="31" spans="1:27" s="5" customFormat="1" ht="19.5">
       <c r="A31" s="8">
         <v>9</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C31" s="8">
         <v>1128</v>
@@ -7019,120 +7026,120 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="5" customFormat="1" ht="19.5">
-      <c r="A32" s="8">
-        <v>9</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="8">
-        <v>1128</v>
-      </c>
-      <c r="D32" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9024</v>
-      </c>
-      <c r="E32" s="10">
-        <v>0</v>
-      </c>
-      <c r="F32" s="8"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10">
-        <f t="shared" si="14"/>
-        <v>9024</v>
-      </c>
-      <c r="I32" s="10">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J32" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9024</v>
-      </c>
-      <c r="K32" s="10">
-        <v>0</v>
-      </c>
-      <c r="L32" s="8"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10">
-        <f t="shared" si="8"/>
-        <v>9024</v>
-      </c>
-      <c r="O32" s="10">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P32" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9024</v>
-      </c>
-      <c r="Q32" s="10">
-        <v>0</v>
-      </c>
-      <c r="R32" s="8"/>
-      <c r="S32" s="10"/>
-      <c r="T32" s="10">
-        <f t="shared" si="10"/>
-        <v>9024</v>
-      </c>
-      <c r="U32" s="10">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V32" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9024</v>
-      </c>
-      <c r="W32" s="10">
-        <v>0</v>
-      </c>
-      <c r="X32" s="8"/>
-      <c r="Y32" s="10"/>
-      <c r="Z32" s="10">
-        <f t="shared" si="12"/>
-        <v>9024</v>
-      </c>
-      <c r="AA32" s="10">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
+    <row r="32" spans="1:27" ht="19.5">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="4"/>
+      <c r="T32" s="11"/>
+      <c r="U32" s="11"/>
+      <c r="V32" s="11"/>
+      <c r="W32" s="5"/>
+      <c r="X32" s="5"/>
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="11"/>
+      <c r="AA32" s="11"/>
     </row>
     <row r="33" spans="1:27" ht="19.5">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="11"/>
-      <c r="U33" s="11"/>
-      <c r="V33" s="11"/>
-      <c r="W33" s="5"/>
-      <c r="X33" s="5"/>
-      <c r="Y33" s="4"/>
-      <c r="Z33" s="11"/>
-      <c r="AA33" s="11"/>
+      <c r="A33" s="8">
+        <v>10</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="8">
+        <v>1222</v>
+      </c>
+      <c r="D33" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9776</v>
+      </c>
+      <c r="E33" s="10">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10">
+        <f>IF((D33-E33)&lt;0,0,(D33-E33))</f>
+        <v>9776</v>
+      </c>
+      <c r="I33" s="10">
+        <f>IF((E33-D33)&lt;0,0,(E33-D33))</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9776</v>
+      </c>
+      <c r="K33" s="10">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10">
+        <f>IF((J33-K33)&lt;0,0,(J33-K33))</f>
+        <v>9776</v>
+      </c>
+      <c r="O33" s="10">
+        <f>IF((K33-J33)&lt;0,0,(K33-J33))</f>
+        <v>0</v>
+      </c>
+      <c r="P33" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9776</v>
+      </c>
+      <c r="Q33" s="10">
+        <v>0</v>
+      </c>
+      <c r="R33" s="8"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10">
+        <f>IF((P33-Q33)&lt;0,0,(P33-Q33))</f>
+        <v>9776</v>
+      </c>
+      <c r="U33" s="10">
+        <f>IF((Q33-P33)&lt;0,0,(Q33-P33))</f>
+        <v>0</v>
+      </c>
+      <c r="V33" s="10">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9776</v>
+      </c>
+      <c r="W33" s="10">
+        <v>0</v>
+      </c>
+      <c r="X33" s="8"/>
+      <c r="Y33" s="10"/>
+      <c r="Z33" s="10">
+        <f>IF((V33-W33)&lt;0,0,(V33-W33))</f>
+        <v>9776</v>
+      </c>
+      <c r="AA33" s="10">
+        <f>IF((W33-V33)&lt;0,0,(W33-V33))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="8">
         <v>10</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C34" s="8">
         <v>1222</v>
@@ -7211,7 +7218,7 @@
         <v>10</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="8">
         <v>1222</v>
@@ -7290,7 +7297,7 @@
         <v>10</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C36" s="8">
         <v>1222</v>
@@ -7369,7 +7376,7 @@
         <v>10</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C37" s="8">
         <v>1222</v>
@@ -7448,7 +7455,7 @@
         <v>10</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C38" s="8">
         <v>1222</v>
@@ -7527,7 +7534,7 @@
         <v>10</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C39" s="8">
         <v>1222</v>
@@ -7606,7 +7613,7 @@
         <v>10</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C40" s="8">
         <v>1222</v>
@@ -7680,12 +7687,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" s="5" customFormat="1" ht="19.5">
       <c r="A41" s="8">
         <v>10</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C41" s="8">
         <v>1222</v>
@@ -7759,132 +7766,136 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="5" customFormat="1" ht="19.5">
-      <c r="A42" s="8">
-        <v>10</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" s="8">
-        <v>1222</v>
-      </c>
-      <c r="D42" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9776</v>
-      </c>
-      <c r="E42" s="10">
-        <v>0</v>
-      </c>
-      <c r="F42" s="8"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10">
-        <f>IF((D42-E42)&lt;0,0,(D42-E42))</f>
-        <v>9776</v>
-      </c>
-      <c r="I42" s="10">
-        <f>IF((E42-D42)&lt;0,0,(E42-D42))</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9776</v>
-      </c>
-      <c r="K42" s="10">
-        <v>0</v>
-      </c>
-      <c r="L42" s="8"/>
-      <c r="M42" s="10"/>
-      <c r="N42" s="10">
-        <f>IF((J42-K42)&lt;0,0,(J42-K42))</f>
-        <v>9776</v>
-      </c>
-      <c r="O42" s="10">
-        <f>IF((K42-J42)&lt;0,0,(K42-J42))</f>
-        <v>0</v>
-      </c>
-      <c r="P42" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9776</v>
-      </c>
-      <c r="Q42" s="10">
-        <v>0</v>
-      </c>
-      <c r="R42" s="8"/>
-      <c r="S42" s="10"/>
-      <c r="T42" s="10">
-        <f>IF((P42-Q42)&lt;0,0,(P42-Q42))</f>
-        <v>9776</v>
-      </c>
-      <c r="U42" s="10">
-        <f>IF((Q42-P42)&lt;0,0,(Q42-P42))</f>
-        <v>0</v>
-      </c>
-      <c r="V42" s="10">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9776</v>
-      </c>
-      <c r="W42" s="10">
-        <v>0</v>
-      </c>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="10"/>
-      <c r="Z42" s="10">
-        <f>IF((V42-W42)&lt;0,0,(V42-W42))</f>
-        <v>9776</v>
-      </c>
-      <c r="AA42" s="10">
-        <f>IF((W42-V42)&lt;0,0,(W42-V42))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:27" ht="19.5">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
+    <row r="42" spans="1:27" ht="19.5">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="11"/>
+      <c r="Q42" s="5"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="4"/>
+      <c r="T42" s="11"/>
+      <c r="U42" s="11"/>
+      <c r="V42" s="11"/>
+      <c r="W42" s="5"/>
+      <c r="X42" s="5"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="11"/>
+      <c r="AA42" s="11"/>
+    </row>
+    <row r="43" spans="1:27" ht="38.25">
+      <c r="A43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="1">
+        <v>822</v>
+      </c>
+      <c r="D43" s="4">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>6576</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4">
+        <f t="shared" si="14"/>
+        <v>6576</v>
+      </c>
+      <c r="I43" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="4">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>6576</v>
+      </c>
+      <c r="K43" s="4">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1"/>
       <c r="M43" s="4"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="11"/>
-      <c r="P43" s="11"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
+      <c r="N43" s="4">
+        <f t="shared" si="8"/>
+        <v>6576</v>
+      </c>
+      <c r="O43" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P43" s="4">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>6576</v>
+      </c>
+      <c r="Q43" s="4">
+        <v>0</v>
+      </c>
+      <c r="R43" s="1"/>
       <c r="S43" s="4"/>
-      <c r="T43" s="11"/>
-      <c r="U43" s="11"/>
-      <c r="V43" s="11"/>
-      <c r="W43" s="5"/>
-      <c r="X43" s="5"/>
+      <c r="T43" s="4">
+        <f t="shared" si="10"/>
+        <v>6576</v>
+      </c>
+      <c r="U43" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V43" s="4">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>6576</v>
+      </c>
+      <c r="W43" s="4">
+        <v>0</v>
+      </c>
+      <c r="X43" s="1"/>
       <c r="Y43" s="4"/>
-      <c r="Z43" s="11"/>
-      <c r="AA43" s="11"/>
-    </row>
-    <row r="44" spans="1:27" ht="38.25">
+      <c r="Z43" s="4">
+        <f t="shared" si="12"/>
+        <v>6576</v>
+      </c>
+      <c r="AA43" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="C44" s="1">
+        <v>822</v>
+      </c>
       <c r="D44" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E44" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0</v>
+      </c>
       <c r="F44" s="1"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="I44" s="4">
         <f t="shared" si="15"/>
@@ -7892,14 +7903,16 @@
       </c>
       <c r="J44" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K44" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="K44" s="4">
+        <v>0</v>
+      </c>
       <c r="L44" s="1"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="O44" s="4">
         <f t="shared" si="9"/>
@@ -7907,14 +7920,16 @@
       </c>
       <c r="P44" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q44" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="Q44" s="4">
+        <v>0</v>
+      </c>
       <c r="R44" s="1"/>
       <c r="S44" s="4"/>
       <c r="T44" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="U44" s="4">
         <f t="shared" si="11"/>
@@ -7922,14 +7937,16 @@
       </c>
       <c r="V44" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W44" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="W44" s="4">
+        <v>0</v>
+      </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="4"/>
       <c r="Z44" s="4">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="13"/>
@@ -7941,19 +7958,23 @@
         <v>19</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="C45" s="1">
+        <v>822</v>
+      </c>
       <c r="D45" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E45" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="E45" s="4">
+        <v>0</v>
+      </c>
       <c r="F45" s="1"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="I45" s="4">
         <f t="shared" si="15"/>
@@ -7961,14 +7982,16 @@
       </c>
       <c r="J45" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K45" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="K45" s="4">
+        <v>0</v>
+      </c>
       <c r="L45" s="1"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="O45" s="4">
         <f t="shared" si="9"/>
@@ -7976,14 +7999,16 @@
       </c>
       <c r="P45" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q45" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="Q45" s="4">
+        <v>0</v>
+      </c>
       <c r="R45" s="1"/>
       <c r="S45" s="4"/>
       <c r="T45" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="U45" s="4">
         <f t="shared" si="11"/>
@@ -7991,14 +8016,16 @@
       </c>
       <c r="V45" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W45" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="W45" s="4">
+        <v>0</v>
+      </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="4"/>
       <c r="Z45" s="4">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="13"/>
@@ -8010,19 +8037,23 @@
         <v>19</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="C46" s="1">
+        <v>822</v>
+      </c>
       <c r="D46" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E46" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="E46" s="4">
+        <v>0</v>
+      </c>
       <c r="F46" s="1"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="I46" s="4">
         <f t="shared" si="15"/>
@@ -8030,14 +8061,16 @@
       </c>
       <c r="J46" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K46" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="K46" s="4">
+        <v>0</v>
+      </c>
       <c r="L46" s="1"/>
       <c r="M46" s="4"/>
       <c r="N46" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="O46" s="4">
         <f t="shared" si="9"/>
@@ -8045,14 +8078,16 @@
       </c>
       <c r="P46" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q46" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="Q46" s="4">
+        <v>0</v>
+      </c>
       <c r="R46" s="1"/>
       <c r="S46" s="4"/>
       <c r="T46" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="U46" s="4">
         <f t="shared" si="11"/>
@@ -8060,38 +8095,44 @@
       </c>
       <c r="V46" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W46" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="W46" s="4">
+        <v>0</v>
+      </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="4"/>
       <c r="Z46" s="4">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="AA46" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.5">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C47" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="C47" s="1">
+        <v>822</v>
+      </c>
       <c r="D47" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E47" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="E47" s="4">
+        <v>0</v>
+      </c>
       <c r="F47" s="1"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="I47" s="4">
         <f t="shared" si="15"/>
@@ -8099,14 +8140,16 @@
       </c>
       <c r="J47" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K47" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="K47" s="4">
+        <v>0</v>
+      </c>
       <c r="L47" s="1"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="O47" s="4">
         <f t="shared" si="9"/>
@@ -8114,14 +8157,16 @@
       </c>
       <c r="P47" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q47" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="Q47" s="4">
+        <v>0</v>
+      </c>
       <c r="R47" s="1"/>
       <c r="S47" s="4"/>
       <c r="T47" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="U47" s="4">
         <f t="shared" si="11"/>
@@ -8129,14 +8174,16 @@
       </c>
       <c r="V47" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W47" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="W47" s="4">
+        <v>0</v>
+      </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="4"/>
       <c r="Z47" s="4">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="AA47" s="4">
         <f t="shared" si="13"/>
@@ -8148,19 +8195,23 @@
         <v>19</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="C48" s="1">
+        <v>822</v>
+      </c>
       <c r="D48" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="E48" s="4">
+        <v>0</v>
+      </c>
       <c r="F48" s="1"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="I48" s="4">
         <f t="shared" si="15"/>
@@ -8168,14 +8219,16 @@
       </c>
       <c r="J48" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K48" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="K48" s="4">
+        <v>0</v>
+      </c>
       <c r="L48" s="1"/>
       <c r="M48" s="4"/>
       <c r="N48" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="O48" s="4">
         <f t="shared" si="9"/>
@@ -8183,14 +8236,16 @@
       </c>
       <c r="P48" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q48" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="Q48" s="4">
+        <v>0</v>
+      </c>
       <c r="R48" s="1"/>
       <c r="S48" s="4"/>
       <c r="T48" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="U48" s="4">
         <f t="shared" si="11"/>
@@ -8198,38 +8253,44 @@
       </c>
       <c r="V48" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W48" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="W48" s="4">
+        <v>0</v>
+      </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="4"/>
       <c r="Z48" s="4">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="AA48" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="38.25">
+    <row r="49" spans="1:27" ht="57.75">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C49" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="C49" s="1">
+        <v>822</v>
+      </c>
       <c r="D49" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E49" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="E49" s="4">
+        <v>0</v>
+      </c>
       <c r="F49" s="1"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="I49" s="4">
         <f t="shared" si="15"/>
@@ -8237,14 +8298,16 @@
       </c>
       <c r="J49" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K49" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="K49" s="4">
+        <v>0</v>
+      </c>
       <c r="L49" s="1"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="O49" s="4">
         <f t="shared" si="9"/>
@@ -8252,14 +8315,16 @@
       </c>
       <c r="P49" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q49" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="Q49" s="4">
+        <v>0</v>
+      </c>
       <c r="R49" s="1"/>
       <c r="S49" s="4"/>
       <c r="T49" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="U49" s="4">
         <f t="shared" si="11"/>
@@ -8267,38 +8332,44 @@
       </c>
       <c r="V49" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W49" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="W49" s="4">
+        <v>0</v>
+      </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="4"/>
       <c r="Z49" s="4">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="AA49" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="57.75">
+    <row r="50" spans="1:27" ht="38.25">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C50" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C50" s="1">
+        <v>822</v>
+      </c>
       <c r="D50" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E50" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="E50" s="4">
+        <v>0</v>
+      </c>
       <c r="F50" s="1"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="I50" s="4">
         <f t="shared" si="15"/>
@@ -8306,14 +8377,16 @@
       </c>
       <c r="J50" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K50" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="K50" s="4">
+        <v>0</v>
+      </c>
       <c r="L50" s="1"/>
       <c r="M50" s="4"/>
       <c r="N50" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="O50" s="4">
         <f t="shared" si="9"/>
@@ -8321,14 +8394,16 @@
       </c>
       <c r="P50" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q50" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="Q50" s="4">
+        <v>0</v>
+      </c>
       <c r="R50" s="1"/>
       <c r="S50" s="4"/>
       <c r="T50" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="U50" s="4">
         <f t="shared" si="11"/>
@@ -8336,1121 +8411,128 @@
       </c>
       <c r="V50" s="4">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W50" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="W50" s="4">
+        <v>0</v>
+      </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="4"/>
       <c r="Z50" s="4">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="AA50" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="38.25">
-      <c r="A51" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E51" s="4"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I51" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J51" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K51" s="4"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O51" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P51" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="1"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U51" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V51" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W51" s="4"/>
-      <c r="X51" s="1"/>
-      <c r="Y51" s="4"/>
-      <c r="Z51" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA51" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:27" s="5" customFormat="1" ht="19.5">
-      <c r="J52" s="11"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="11"/>
-      <c r="P52" s="11"/>
-      <c r="T52" s="11"/>
-      <c r="U52" s="11"/>
-      <c r="V52" s="11"/>
-      <c r="Z52" s="11"/>
-      <c r="AA52" s="11"/>
-    </row>
-    <row r="53" spans="1:27" ht="19.5">
-      <c r="A53" s="1"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I53" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J53" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K53" s="4"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O53" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P53" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="1"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U53" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V53" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W53" s="4"/>
-      <c r="X53" s="1"/>
-      <c r="Y53" s="4"/>
-      <c r="Z53" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA53" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:27" ht="19.5">
-      <c r="A54" s="1"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I54" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J54" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K54" s="4"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O54" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P54" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="1"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U54" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V54" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W54" s="4"/>
-      <c r="X54" s="1"/>
-      <c r="Y54" s="4"/>
-      <c r="Z54" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA54" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:27" ht="19.5">
-      <c r="A55" s="1"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I55" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J55" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K55" s="4"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O55" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P55" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="1"/>
-      <c r="S55" s="4"/>
-      <c r="T55" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U55" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V55" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W55" s="4"/>
-      <c r="X55" s="1"/>
-      <c r="Y55" s="4"/>
-      <c r="Z55" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA55" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:27" ht="19.5">
-      <c r="A56" s="1"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I56" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K56" s="4"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O56" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P56" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="1"/>
-      <c r="S56" s="4"/>
-      <c r="T56" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U56" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V56" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W56" s="4"/>
-      <c r="X56" s="1"/>
-      <c r="Y56" s="4"/>
-      <c r="Z56" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA56" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:27" ht="19.5">
-      <c r="A57" s="1"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I57" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K57" s="4"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O57" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P57" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="1"/>
-      <c r="S57" s="4"/>
-      <c r="T57" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U57" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V57" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W57" s="4"/>
-      <c r="X57" s="1"/>
-      <c r="Y57" s="4"/>
-      <c r="Z57" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA57" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:27" ht="19.5">
-      <c r="A58" s="1"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I58" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K58" s="4"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O58" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P58" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="1"/>
-      <c r="S58" s="4"/>
-      <c r="T58" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V58" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W58" s="4"/>
-      <c r="X58" s="1"/>
-      <c r="Y58" s="4"/>
-      <c r="Z58" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA58" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:27" ht="19.5">
-      <c r="A59" s="1"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I59" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K59" s="4"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O59" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P59" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q59" s="4"/>
-      <c r="R59" s="1"/>
-      <c r="S59" s="4"/>
-      <c r="T59" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U59" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V59" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W59" s="4"/>
-      <c r="X59" s="1"/>
-      <c r="Y59" s="4"/>
-      <c r="Z59" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA59" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:27" ht="19.5">
-      <c r="A60" s="1"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I60" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K60" s="4"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O60" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P60" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q60" s="4"/>
-      <c r="R60" s="1"/>
-      <c r="S60" s="4"/>
-      <c r="T60" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U60" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V60" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W60" s="4"/>
-      <c r="X60" s="1"/>
-      <c r="Y60" s="4"/>
-      <c r="Z60" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA60" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:27" ht="19.5">
-      <c r="A61" s="1"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I61" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K61" s="4"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O61" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P61" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q61" s="4"/>
-      <c r="R61" s="1"/>
-      <c r="S61" s="4"/>
-      <c r="T61" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U61" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V61" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W61" s="4"/>
-      <c r="X61" s="1"/>
-      <c r="Y61" s="4"/>
-      <c r="Z61" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA61" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:27" s="5" customFormat="1" ht="19.5">
-      <c r="A62" s="1"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I62" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J62" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K62" s="4"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O62" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P62" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="1"/>
-      <c r="S62" s="4"/>
-      <c r="T62" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U62" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V62" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W62" s="4"/>
-      <c r="X62" s="1"/>
-      <c r="Y62" s="4"/>
-      <c r="Z62" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA62" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:27" ht="19.5">
-      <c r="A63" s="1"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I63" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J63" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K63" s="4"/>
-      <c r="L63" s="1"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O63" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P63" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q63" s="4"/>
-      <c r="R63" s="1"/>
-      <c r="S63" s="4"/>
-      <c r="T63" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U63" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V63" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W63" s="4"/>
-      <c r="X63" s="1"/>
-      <c r="Y63" s="4"/>
-      <c r="Z63" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA63" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27" ht="19.5">
-      <c r="A64" s="1"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I64" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J64" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K64" s="4"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="4"/>
-      <c r="N64" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O64" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P64" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q64" s="4"/>
-      <c r="R64" s="1"/>
-      <c r="S64" s="4"/>
-      <c r="T64" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U64" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V64" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W64" s="4"/>
-      <c r="X64" s="1"/>
-      <c r="Y64" s="4"/>
-      <c r="Z64" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA64" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:27" ht="19.5">
-      <c r="A65" s="1"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I65" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J65" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K65" s="4"/>
-      <c r="L65" s="1"/>
-      <c r="M65" s="4"/>
-      <c r="N65" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O65" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P65" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q65" s="4"/>
-      <c r="R65" s="1"/>
-      <c r="S65" s="4"/>
-      <c r="T65" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U65" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V65" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W65" s="4"/>
-      <c r="X65" s="1"/>
-      <c r="Y65" s="4"/>
-      <c r="Z65" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA65" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:27" ht="19.5">
-      <c r="A66" s="1"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I66" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J66" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K66" s="4"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O66" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P66" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="1"/>
-      <c r="S66" s="4"/>
-      <c r="T66" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U66" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V66" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W66" s="4"/>
-      <c r="X66" s="1"/>
-      <c r="Y66" s="4"/>
-      <c r="Z66" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA66" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:27" ht="19.5">
-      <c r="A67" s="1"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="1"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I67" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K67" s="4"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O67" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P67" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="1"/>
-      <c r="S67" s="4"/>
-      <c r="T67" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U67" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V67" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W67" s="4"/>
-      <c r="X67" s="1"/>
-      <c r="Y67" s="4"/>
-      <c r="Z67" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA67" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:27" ht="19.5">
-      <c r="A68" s="27"/>
-      <c r="B68" s="28"/>
-      <c r="C68" s="27"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="27"/>
-      <c r="G68" s="29"/>
-      <c r="H68" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="I68" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J68" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K68" s="29"/>
-      <c r="L68" s="27"/>
-      <c r="M68" s="29"/>
-      <c r="N68" s="4">
-        <f t="shared" ref="N68" si="16">IF((J68-K68)&lt;0,0,(J68-K68))</f>
-        <v>0</v>
-      </c>
-      <c r="O68" s="4">
-        <f t="shared" ref="O68" si="17">IF((K68-J68)&lt;0,0,(K68-J68))</f>
-        <v>0</v>
-      </c>
-      <c r="P68" s="4"/>
-      <c r="Q68" s="29"/>
-      <c r="R68" s="27"/>
-      <c r="S68" s="29"/>
-      <c r="T68" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U68" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V68" s="4">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W68" s="29"/>
-      <c r="X68" s="27"/>
-      <c r="Y68" s="29"/>
-      <c r="Z68" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA68" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
+    <row r="51" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A51"/>
+      <c r="B51"/>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51"/>
+      <c r="K51"/>
+      <c r="L51"/>
+      <c r="M51"/>
+      <c r="N51"/>
+      <c r="O51"/>
+      <c r="P51"/>
+      <c r="Q51"/>
+      <c r="R51"/>
+      <c r="S51"/>
+      <c r="T51"/>
+      <c r="U51"/>
+      <c r="V51"/>
+      <c r="W51"/>
+      <c r="X51"/>
+      <c r="Y51"/>
+      <c r="Z51"/>
+      <c r="AA51"/>
+    </row>
+    <row r="52" spans="1:27" ht="15"/>
+    <row r="53" spans="1:27" ht="15"/>
+    <row r="54" spans="1:27" ht="15"/>
+    <row r="55" spans="1:27" ht="15"/>
+    <row r="56" spans="1:27" ht="15"/>
+    <row r="57" spans="1:27" ht="15"/>
+    <row r="58" spans="1:27" ht="15"/>
+    <row r="59" spans="1:27" ht="15"/>
+    <row r="60" spans="1:27" ht="15"/>
+    <row r="61" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A61"/>
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61"/>
+      <c r="G61"/>
+      <c r="H61"/>
+      <c r="I61"/>
+      <c r="J61"/>
+      <c r="K61"/>
+      <c r="L61"/>
+      <c r="M61"/>
+      <c r="N61"/>
+      <c r="O61"/>
+      <c r="P61"/>
+      <c r="Q61"/>
+      <c r="R61"/>
+      <c r="S61"/>
+      <c r="T61"/>
+      <c r="U61"/>
+      <c r="V61"/>
+      <c r="W61"/>
+      <c r="X61"/>
+      <c r="Y61"/>
+      <c r="Z61"/>
+      <c r="AA61"/>
+    </row>
+    <row r="62" spans="1:27" ht="15"/>
+    <row r="63" spans="1:27" ht="15"/>
+    <row r="64" spans="1:27" ht="15"/>
+    <row r="65" spans="1:27" ht="15"/>
+    <row r="66" spans="1:27" ht="15"/>
+    <row r="67" spans="1:27" ht="15"/>
+    <row r="68" spans="1:27" ht="15"/>
     <row r="69" spans="1:27" ht="15"/>
     <row r="70" spans="1:27" ht="15"/>
-    <row r="71" spans="1:27" ht="15"/>
-    <row r="72" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A72"/>
-      <c r="B72"/>
-      <c r="C72"/>
-      <c r="D72"/>
-      <c r="E72"/>
-      <c r="F72"/>
-      <c r="G72"/>
-      <c r="H72"/>
-      <c r="I72"/>
-      <c r="J72"/>
-      <c r="K72"/>
-      <c r="L72"/>
-      <c r="M72"/>
-      <c r="N72"/>
-      <c r="O72"/>
-      <c r="P72"/>
-      <c r="Q72"/>
-      <c r="R72"/>
-      <c r="S72"/>
-      <c r="T72"/>
-      <c r="U72"/>
-      <c r="V72"/>
-      <c r="W72"/>
-      <c r="X72"/>
-      <c r="Y72"/>
-      <c r="Z72"/>
-      <c r="AA72"/>
-    </row>
+    <row r="71" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A71"/>
+      <c r="B71"/>
+      <c r="C71"/>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71"/>
+      <c r="G71"/>
+      <c r="H71"/>
+      <c r="I71"/>
+      <c r="J71"/>
+      <c r="K71"/>
+      <c r="L71"/>
+      <c r="M71"/>
+      <c r="N71"/>
+      <c r="O71"/>
+      <c r="P71"/>
+      <c r="Q71"/>
+      <c r="R71"/>
+      <c r="S71"/>
+      <c r="T71"/>
+      <c r="U71"/>
+      <c r="V71"/>
+      <c r="W71"/>
+      <c r="X71"/>
+      <c r="Y71"/>
+      <c r="Z71"/>
+      <c r="AA71"/>
+    </row>
+    <row r="72" spans="1:27" ht="15"/>
     <row r="73" spans="1:27" ht="15"/>
     <row r="74" spans="1:27" ht="15"/>
     <row r="75" spans="1:27" ht="15"/>
@@ -9459,36 +8541,36 @@
     <row r="78" spans="1:27" ht="15"/>
     <row r="79" spans="1:27" ht="15"/>
     <row r="80" spans="1:27" ht="15"/>
-    <row r="81" spans="1:27" ht="15"/>
-    <row r="82" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A82"/>
-      <c r="B82"/>
-      <c r="C82"/>
-      <c r="D82"/>
-      <c r="E82"/>
-      <c r="F82"/>
-      <c r="G82"/>
-      <c r="H82"/>
-      <c r="I82"/>
-      <c r="J82"/>
-      <c r="K82"/>
-      <c r="L82"/>
-      <c r="M82"/>
-      <c r="N82"/>
-      <c r="O82"/>
-      <c r="P82"/>
-      <c r="Q82"/>
-      <c r="R82"/>
-      <c r="S82"/>
-      <c r="T82"/>
-      <c r="U82"/>
-      <c r="V82"/>
-      <c r="W82"/>
-      <c r="X82"/>
-      <c r="Y82"/>
-      <c r="Z82"/>
-      <c r="AA82"/>
-    </row>
+    <row r="81" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A81"/>
+      <c r="B81"/>
+      <c r="C81"/>
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="F81"/>
+      <c r="G81"/>
+      <c r="H81"/>
+      <c r="I81"/>
+      <c r="J81"/>
+      <c r="K81"/>
+      <c r="L81"/>
+      <c r="M81"/>
+      <c r="N81"/>
+      <c r="O81"/>
+      <c r="P81"/>
+      <c r="Q81"/>
+      <c r="R81"/>
+      <c r="S81"/>
+      <c r="T81"/>
+      <c r="U81"/>
+      <c r="V81"/>
+      <c r="W81"/>
+      <c r="X81"/>
+      <c r="Y81"/>
+      <c r="Z81"/>
+      <c r="AA81"/>
+    </row>
+    <row r="82" spans="1:27" ht="15"/>
     <row r="83" spans="1:27" ht="15"/>
     <row r="84" spans="1:27" ht="15"/>
     <row r="85" spans="1:27" ht="15"/>
@@ -9497,36 +8579,36 @@
     <row r="88" spans="1:27" ht="15"/>
     <row r="89" spans="1:27" ht="15"/>
     <row r="90" spans="1:27" ht="15"/>
-    <row r="91" spans="1:27" ht="15"/>
-    <row r="92" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A92"/>
-      <c r="B92"/>
-      <c r="C92"/>
-      <c r="D92"/>
-      <c r="E92"/>
-      <c r="F92"/>
-      <c r="G92"/>
-      <c r="H92"/>
-      <c r="I92"/>
-      <c r="J92"/>
-      <c r="K92"/>
-      <c r="L92"/>
-      <c r="M92"/>
-      <c r="N92"/>
-      <c r="O92"/>
-      <c r="P92"/>
-      <c r="Q92"/>
-      <c r="R92"/>
-      <c r="S92"/>
-      <c r="T92"/>
-      <c r="U92"/>
-      <c r="V92"/>
-      <c r="W92"/>
-      <c r="X92"/>
-      <c r="Y92"/>
-      <c r="Z92"/>
-      <c r="AA92"/>
-    </row>
+    <row r="91" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A91"/>
+      <c r="B91"/>
+      <c r="C91"/>
+      <c r="D91"/>
+      <c r="E91"/>
+      <c r="F91"/>
+      <c r="G91"/>
+      <c r="H91"/>
+      <c r="I91"/>
+      <c r="J91"/>
+      <c r="K91"/>
+      <c r="L91"/>
+      <c r="M91"/>
+      <c r="N91"/>
+      <c r="O91"/>
+      <c r="P91"/>
+      <c r="Q91"/>
+      <c r="R91"/>
+      <c r="S91"/>
+      <c r="T91"/>
+      <c r="U91"/>
+      <c r="V91"/>
+      <c r="W91"/>
+      <c r="X91"/>
+      <c r="Y91"/>
+      <c r="Z91"/>
+      <c r="AA91"/>
+    </row>
+    <row r="92" spans="1:27" ht="15"/>
     <row r="93" spans="1:27" ht="15"/>
     <row r="94" spans="1:27" ht="15"/>
     <row r="95" spans="1:27" ht="15"/>
@@ -9535,36 +8617,36 @@
     <row r="98" spans="1:27" ht="15"/>
     <row r="99" spans="1:27" ht="15"/>
     <row r="100" spans="1:27" ht="15"/>
-    <row r="101" spans="1:27" ht="15"/>
-    <row r="102" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A102"/>
-      <c r="B102"/>
-      <c r="C102"/>
-      <c r="D102"/>
-      <c r="E102"/>
-      <c r="F102"/>
-      <c r="G102"/>
-      <c r="H102"/>
-      <c r="I102"/>
-      <c r="J102"/>
-      <c r="K102"/>
-      <c r="L102"/>
-      <c r="M102"/>
-      <c r="N102"/>
-      <c r="O102"/>
-      <c r="P102"/>
-      <c r="Q102"/>
-      <c r="R102"/>
-      <c r="S102"/>
-      <c r="T102"/>
-      <c r="U102"/>
-      <c r="V102"/>
-      <c r="W102"/>
-      <c r="X102"/>
-      <c r="Y102"/>
-      <c r="Z102"/>
-      <c r="AA102"/>
-    </row>
+    <row r="101" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101"/>
+      <c r="I101"/>
+      <c r="J101"/>
+      <c r="K101"/>
+      <c r="L101"/>
+      <c r="M101"/>
+      <c r="N101"/>
+      <c r="O101"/>
+      <c r="P101"/>
+      <c r="Q101"/>
+      <c r="R101"/>
+      <c r="S101"/>
+      <c r="T101"/>
+      <c r="U101"/>
+      <c r="V101"/>
+      <c r="W101"/>
+      <c r="X101"/>
+      <c r="Y101"/>
+      <c r="Z101"/>
+      <c r="AA101"/>
+    </row>
+    <row r="102" spans="1:27" ht="15"/>
     <row r="103" spans="1:27" ht="15"/>
     <row r="104" spans="1:27" ht="15"/>
     <row r="105" spans="1:27" ht="15"/>
@@ -9572,36 +8654,36 @@
     <row r="107" spans="1:27" ht="15"/>
     <row r="108" spans="1:27" ht="15"/>
     <row r="109" spans="1:27" ht="15"/>
-    <row r="110" spans="1:27" ht="15"/>
-    <row r="111" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A111"/>
-      <c r="B111"/>
-      <c r="C111"/>
-      <c r="D111"/>
-      <c r="E111"/>
-      <c r="F111"/>
-      <c r="G111"/>
-      <c r="H111"/>
-      <c r="I111"/>
-      <c r="J111"/>
-      <c r="K111"/>
-      <c r="L111"/>
-      <c r="M111"/>
-      <c r="N111"/>
-      <c r="O111"/>
-      <c r="P111"/>
-      <c r="Q111"/>
-      <c r="R111"/>
-      <c r="S111"/>
-      <c r="T111"/>
-      <c r="U111"/>
-      <c r="V111"/>
-      <c r="W111"/>
-      <c r="X111"/>
-      <c r="Y111"/>
-      <c r="Z111"/>
-      <c r="AA111"/>
-    </row>
+    <row r="110" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+      <c r="D110"/>
+      <c r="E110"/>
+      <c r="F110"/>
+      <c r="G110"/>
+      <c r="H110"/>
+      <c r="I110"/>
+      <c r="J110"/>
+      <c r="K110"/>
+      <c r="L110"/>
+      <c r="M110"/>
+      <c r="N110"/>
+      <c r="O110"/>
+      <c r="P110"/>
+      <c r="Q110"/>
+      <c r="R110"/>
+      <c r="S110"/>
+      <c r="T110"/>
+      <c r="U110"/>
+      <c r="V110"/>
+      <c r="W110"/>
+      <c r="X110"/>
+      <c r="Y110"/>
+      <c r="Z110"/>
+      <c r="AA110"/>
+    </row>
+    <row r="111" spans="1:27" ht="15"/>
     <row r="112" spans="1:27" ht="15"/>
     <row r="113" ht="15"/>
     <row r="114" ht="15"/>
@@ -9617,16 +8699,16 @@
     <row r="124" ht="15"/>
     <row r="125" ht="15"/>
     <row r="126" ht="15"/>
-    <row r="127" ht="15"/>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C44:C51 C53:C68 C2" name="Textbooks"/>
-    <protectedRange sqref="D2:F2 H44:I51 Q44:R51 W44:X51 D53:F68 H53:I68 N68:R68 W53:X68 J3:J68 V2:X2 Q53:R67 P2:R2 Z3:AA68 N3:P67 T3:V68 K44:L51 K53:L68 H4:I12 H14:I22 H24:I32 H34:I42 D44:F51 J2:L2 D4:F12 D14:F22 D24:F32 D34:F42 K4:L12 K14:L22 K24:L32 K34:L42 Q4:R12 Q14:R22 Q24:R32 Q34:R42 W4:X12 W14:X22 W24:X32 W34:X42" name="LAS"/>
-    <protectedRange sqref="S2:U2 M2:O2 Y2:AA2 Y3:Y51 G53:G68 M53:M68 S53:S68 Y53:Y68 G24:G32 S3:S51 G34:G42 G44:G51 M3:M51 G4:G12 G2:I2 G14:G22" name="SOURCE"/>
-    <protectedRange sqref="C4:C12" name="Textbooks_1"/>
-    <protectedRange sqref="C14:C22" name="Textbooks_2"/>
-    <protectedRange sqref="C24:C32" name="Textbooks_3"/>
-    <protectedRange sqref="C34:C42" name="Textbooks_4"/>
+    <protectedRange sqref="C2" name="Textbooks"/>
+    <protectedRange sqref="H43:I50 W23:X31 W33:X41 D43:F50 J3:J50 K43:L50 V2:X2 Z3:AA50 P2:R2 N3:P50 T3:V50 Q43:R50 W43:X50 H3:I11 H13:I21 H23:I31 H33:I41 J2:L2 D2:F11 D13:F21 D23:F31 D33:F41 K3:L11 K13:L21 K23:L31 K33:L41 Q3:R11 Q13:R21 Q23:R31 Q33:R41 W3:X11 W13:X21" name="LAS"/>
+    <protectedRange sqref="S2:U2 M2:O2 Y2:AA2 Y3:Y50 M3:M50 G3:G11 G2:I2 G13:G21 G23:G31 S3:S50 G33:G41 G43:G50" name="SOURCE"/>
+    <protectedRange sqref="C3:C11" name="Textbooks_1"/>
+    <protectedRange sqref="C13:C21" name="Textbooks_2"/>
+    <protectedRange sqref="C23:C31" name="Textbooks_3"/>
+    <protectedRange sqref="C33:C41" name="Textbooks_4"/>
+    <protectedRange sqref="C43:C50" name="Textbooks_5"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -9635,14 +8717,11 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S53:S68 M53:M68 Y53:Y68 G53:G68" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
-      <formula1>"CO,RO,SDO"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X53:X68 F4:F12 F14:F22 F24:F32 F34:F42 F44:F51 F53:F68 L4:L12 L14:L22 L24:L32 L34:L42 L44:L51 L53:L68 R4:R12 R14:R22 R24:R32 R34:R42 R44:R51 R53:R68 X4:X12 X14:X22 X24:X32 X34:X42 X44:X51" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F11 F13:F21 F23:F31 F33:F41 F43:F50 L3:L11 L13:L21 L23:L31 L33:L41 L43:L50 R3:R11 R13:R21 R23:R31 R33:R41 R43:R50 X3:X11 X13:X21 X23:X31 X33:X41 X43:X50" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G12 M3:M51 G24:G32 G34:G42 G44:G51 S3:S51 Y3:Y51 G14:G22" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G11 G23:G31 G33:G41 G43:G50 G13:G21 Y3:Y50 S3:S50 M3:M50" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9655,7 +8734,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB140"/>
+  <dimension ref="A1:AB139"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -9684,45 +8763,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="26" customFormat="1" ht="34.15" customHeight="1">
-      <c r="B1" s="30"/>
-      <c r="D1" s="35" t="s">
+      <c r="B1" s="27"/>
+      <c r="D1" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="36" t="s">
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="37" t="s">
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="38" t="s">
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
-      <c r="Z1" s="38"/>
-      <c r="AA1" s="38"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="28" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="14" t="s">
@@ -9755,10 +8834,10 @@
       <c r="L2" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="N2" s="33" t="s">
+      <c r="N2" s="30" t="s">
         <v>67</v>
       </c>
       <c r="O2" s="20" t="s">
@@ -9791,51 +8870,101 @@
       <c r="X2" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="Y2" s="34" t="s">
+      <c r="Y2" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="Z2" s="34" t="s">
+      <c r="Z2" s="31" t="s">
         <v>79</v>
       </c>
       <c r="AA2" s="24" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
+    <row r="3" spans="1:27" ht="19.5">
+      <c r="A3" s="8">
+        <v>7</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="8">
+        <v>1499</v>
+      </c>
+      <c r="D3" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11992</v>
+      </c>
+      <c r="E3" s="10">
+        <v>0</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10">
+        <f t="shared" ref="H3:H19" si="0">IF((D3-E3)&lt;0,0,(D3-E3))</f>
+        <v>11992</v>
+      </c>
+      <c r="I3" s="10">
+        <f t="shared" ref="I3:I19" si="1">IF((E3-D3)&lt;0,0,(E3-D3))</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11992</v>
+      </c>
+      <c r="K3" s="10">
+        <v>0</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10">
+        <f t="shared" ref="N3:N6" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
+        <v>11992</v>
+      </c>
+      <c r="O3" s="10">
+        <f t="shared" ref="O3:O6" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11992</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10">
+        <f t="shared" ref="T3:T8" si="4">IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
+        <v>11992</v>
+      </c>
+      <c r="U3" s="10">
+        <f t="shared" ref="U3:U8" si="5">IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
+        <v>0</v>
+      </c>
+      <c r="V3" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11992</v>
+      </c>
+      <c r="W3" s="10">
+        <v>0</v>
+      </c>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10">
+        <f t="shared" ref="Z3:Z8" si="6">IF((V3-W3)&lt;0,0,(V3-W3))</f>
+        <v>11992</v>
+      </c>
+      <c r="AA3" s="10">
+        <f t="shared" ref="AA3:AA8" si="7">IF((W3-V3)&lt;0,0,(W3-V3))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="8">
         <v>7</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" s="8">
         <v>1499</v>
@@ -9850,11 +8979,11 @@
       <c r="F4" s="8"/>
       <c r="G4" s="10"/>
       <c r="H4" s="10">
-        <f t="shared" ref="H4:H20" si="0">IF((D4-E4)&lt;0,0,(D4-E4))</f>
+        <f t="shared" si="0"/>
         <v>11992</v>
       </c>
       <c r="I4" s="10">
-        <f t="shared" ref="I4:I20" si="1">IF((E4-D4)&lt;0,0,(E4-D4))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J4" s="10">
@@ -9867,11 +8996,11 @@
       <c r="L4" s="8"/>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
-        <f t="shared" ref="N4:N7" si="2">IF((J4-K4)&lt;0,0,(J4-K4))</f>
+        <f t="shared" si="2"/>
         <v>11992</v>
       </c>
       <c r="O4" s="10">
-        <f t="shared" ref="O4:O7" si="3">IF((K4-J4)&lt;0,0,(K4-J4))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P4" s="10">
@@ -9884,11 +9013,11 @@
       <c r="R4" s="8"/>
       <c r="S4" s="10"/>
       <c r="T4" s="10">
-        <f t="shared" ref="T4:T9" si="4">IF((P4-Q4)&lt;0,0,(P4-Q4))</f>
+        <f t="shared" si="4"/>
         <v>11992</v>
       </c>
       <c r="U4" s="10">
-        <f t="shared" ref="U4:U9" si="5">IF((Q4-P4)&lt;0,0,(Q4-P4))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V4" s="10">
@@ -9901,11 +9030,11 @@
       <c r="X4" s="8"/>
       <c r="Y4" s="10"/>
       <c r="Z4" s="10">
-        <f t="shared" ref="Z4:Z9" si="6">IF((V4-W4)&lt;0,0,(V4-W4))</f>
+        <f t="shared" si="6"/>
         <v>11992</v>
       </c>
       <c r="AA4" s="10">
-        <f t="shared" ref="AA4:AA9" si="7">IF((W4-V4)&lt;0,0,(W4-V4))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -9914,7 +9043,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="8">
         <v>1499</v>
@@ -9993,7 +9122,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="8">
         <v>1499</v>
@@ -10067,12 +9196,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="38.25">
       <c r="A7" s="8">
         <v>7</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="8">
         <v>1499</v>
@@ -10104,11 +9233,11 @@
       <c r="L7" s="8"/>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="N7:N13" si="8">IF((J7-K7)&lt;0,0,(J7-K7))</f>
         <v>11992</v>
       </c>
       <c r="O7" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="O7:O13" si="9">IF((K7-J7)&lt;0,0,(K7-J7))</f>
         <v>0</v>
       </c>
       <c r="P7" s="10">
@@ -10146,12 +9275,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="38.25">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="8">
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="8">
         <v>1499</v>
@@ -10183,11 +9312,11 @@
       <c r="L8" s="8"/>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
-        <f t="shared" ref="N8:N14" si="8">IF((J8-K8)&lt;0,0,(J8-K8))</f>
+        <f t="shared" si="8"/>
         <v>11992</v>
       </c>
       <c r="O8" s="10">
-        <f t="shared" ref="O8:O14" si="9">IF((K8-J8)&lt;0,0,(K8-J8))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P8" s="10">
@@ -10226,11 +9355,11 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="19.5">
-      <c r="A9" s="8">
+      <c r="A9" s="29">
         <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="C9" s="8">
         <v>1499</v>
@@ -10245,11 +9374,11 @@
       <c r="F9" s="8"/>
       <c r="G9" s="10"/>
       <c r="H9" s="10">
-        <f t="shared" si="0"/>
+        <f>IF((D9-E9)&lt;0,0,(D9-E9))</f>
         <v>11992</v>
       </c>
       <c r="I9" s="10">
-        <f t="shared" si="1"/>
+        <f>IF((E9-D9)&lt;0,0,(E9-D9))</f>
         <v>0</v>
       </c>
       <c r="J9" s="10">
@@ -10279,11 +9408,11 @@
       <c r="R9" s="8"/>
       <c r="S9" s="10"/>
       <c r="T9" s="10">
-        <f t="shared" si="4"/>
+        <f>IF((P9-Q9)&lt;0,0,(P9-Q9))</f>
         <v>11992</v>
       </c>
       <c r="U9" s="10">
-        <f t="shared" si="5"/>
+        <f>IF((Q9-P9)&lt;0,0,(Q9-P9))</f>
         <v>0</v>
       </c>
       <c r="V9" s="10">
@@ -10296,20 +9425,20 @@
       <c r="X9" s="8"/>
       <c r="Y9" s="10"/>
       <c r="Z9" s="10">
-        <f t="shared" si="6"/>
+        <f>IF((V9-W9)&lt;0,0,(V9-W9))</f>
         <v>11992</v>
       </c>
       <c r="AA9" s="10">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="19.5">
-      <c r="A10" s="32">
+        <f>IF((W9-V9)&lt;0,0,(W9-V9))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" s="5" customFormat="1" ht="19.5">
+      <c r="A10" s="8">
         <v>7</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" s="8">
         <v>1499</v>
@@ -10324,11 +9453,11 @@
       <c r="F10" s="8"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10">
-        <f>IF((D10-E10)&lt;0,0,(D10-E10))</f>
+        <f t="shared" si="0"/>
         <v>11992</v>
       </c>
       <c r="I10" s="10">
-        <f>IF((E10-D10)&lt;0,0,(E10-D10))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J10" s="10">
@@ -10358,11 +9487,11 @@
       <c r="R10" s="8"/>
       <c r="S10" s="10"/>
       <c r="T10" s="10">
-        <f>IF((P10-Q10)&lt;0,0,(P10-Q10))</f>
+        <f t="shared" ref="T10:T58" si="10">IF((P10-Q10)&lt;0,0,(P10-Q10))</f>
         <v>11992</v>
       </c>
       <c r="U10" s="10">
-        <f>IF((Q10-P10)&lt;0,0,(Q10-P10))</f>
+        <f t="shared" ref="U10:U58" si="11">IF((Q10-P10)&lt;0,0,(Q10-P10))</f>
         <v>0</v>
       </c>
       <c r="V10" s="10">
@@ -10375,20 +9504,20 @@
       <c r="X10" s="8"/>
       <c r="Y10" s="10"/>
       <c r="Z10" s="10">
-        <f>IF((V10-W10)&lt;0,0,(V10-W10))</f>
+        <f t="shared" ref="Z10:Z58" si="12">IF((V10-W10)&lt;0,0,(V10-W10))</f>
         <v>11992</v>
       </c>
       <c r="AA10" s="10">
-        <f>IF((W10-V10)&lt;0,0,(W10-V10))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" s="5" customFormat="1" ht="19.5">
+        <f t="shared" ref="AA10:AA58" si="13">IF((W10-V10)&lt;0,0,(W10-V10))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="19.5">
       <c r="A11" s="8">
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="C11" s="8">
         <v>1499</v>
@@ -10437,11 +9566,11 @@
       <c r="R11" s="8"/>
       <c r="S11" s="10"/>
       <c r="T11" s="10">
-        <f t="shared" ref="T11:T59" si="10">IF((P11-Q11)&lt;0,0,(P11-Q11))</f>
+        <f t="shared" si="10"/>
         <v>11992</v>
       </c>
       <c r="U11" s="10">
-        <f t="shared" ref="U11:U59" si="11">IF((Q11-P11)&lt;0,0,(Q11-P11))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V11" s="10">
@@ -10454,20 +9583,20 @@
       <c r="X11" s="8"/>
       <c r="Y11" s="10"/>
       <c r="Z11" s="10">
-        <f t="shared" ref="Z11:Z59" si="12">IF((V11-W11)&lt;0,0,(V11-W11))</f>
+        <f t="shared" si="12"/>
         <v>11992</v>
       </c>
       <c r="AA11" s="10">
-        <f t="shared" ref="AA11:AA59" si="13">IF((W11-V11)&lt;0,0,(W11-V11))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="19.5">
-      <c r="A12" s="8">
+      <c r="A12" s="29">
         <v>7</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C12" s="8">
         <v>1499</v>
@@ -10482,11 +9611,11 @@
       <c r="F12" s="8"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10">
-        <f t="shared" si="0"/>
+        <f>IF((D12-E12)&lt;0,0,(D12-E12))</f>
         <v>11992</v>
       </c>
       <c r="I12" s="10">
-        <f t="shared" si="1"/>
+        <f>IF((E12-D12)&lt;0,0,(E12-D12))</f>
         <v>0</v>
       </c>
       <c r="J12" s="10">
@@ -10516,11 +9645,11 @@
       <c r="R12" s="8"/>
       <c r="S12" s="10"/>
       <c r="T12" s="10">
-        <f t="shared" si="10"/>
+        <f>IF((P12-Q12)&lt;0,0,(P12-Q12))</f>
         <v>11992</v>
       </c>
       <c r="U12" s="10">
-        <f t="shared" si="11"/>
+        <f>IF((Q12-P12)&lt;0,0,(Q12-P12))</f>
         <v>0</v>
       </c>
       <c r="V12" s="10">
@@ -10533,20 +9662,20 @@
       <c r="X12" s="8"/>
       <c r="Y12" s="10"/>
       <c r="Z12" s="10">
-        <f t="shared" si="12"/>
+        <f>IF((V12-W12)&lt;0,0,(V12-W12))</f>
         <v>11992</v>
       </c>
       <c r="AA12" s="10">
-        <f t="shared" si="13"/>
+        <f>IF((W12-V12)&lt;0,0,(W12-V12))</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="19.5">
-      <c r="A13" s="32">
+      <c r="A13" s="8">
         <v>7</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" s="8">
         <v>1499</v>
@@ -10561,11 +9690,11 @@
       <c r="F13" s="8"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10">
-        <f>IF((D13-E13)&lt;0,0,(D13-E13))</f>
+        <f t="shared" si="0"/>
         <v>11992</v>
       </c>
       <c r="I13" s="10">
-        <f>IF((E13-D13)&lt;0,0,(E13-D13))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J13" s="10">
@@ -10595,11 +9724,11 @@
       <c r="R13" s="8"/>
       <c r="S13" s="10"/>
       <c r="T13" s="10">
-        <f>IF((P13-Q13)&lt;0,0,(P13-Q13))</f>
+        <f t="shared" si="10"/>
         <v>11992</v>
       </c>
       <c r="U13" s="10">
-        <f>IF((Q13-P13)&lt;0,0,(Q13-P13))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V13" s="10">
@@ -10612,128 +9741,128 @@
       <c r="X13" s="8"/>
       <c r="Y13" s="10"/>
       <c r="Z13" s="10">
-        <f>IF((V13-W13)&lt;0,0,(V13-W13))</f>
+        <f t="shared" si="12"/>
         <v>11992</v>
       </c>
       <c r="AA13" s="10">
-        <f>IF((W13-V13)&lt;0,0,(W13-V13))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="19.5">
-      <c r="A14" s="8">
-        <v>7</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" s="8">
-        <v>1499</v>
-      </c>
-      <c r="D14" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11992</v>
-      </c>
-      <c r="E14" s="10">
-        <v>0</v>
-      </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="15">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+      <c r="AA14" s="5"/>
+    </row>
+    <row r="15" spans="1:27" ht="19.5">
+      <c r="A15" s="8">
+        <v>8</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="8">
+        <v>1450</v>
+      </c>
+      <c r="D15" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11600</v>
+      </c>
+      <c r="E15" s="10">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10">
         <f t="shared" si="0"/>
-        <v>11992</v>
-      </c>
-      <c r="I14" s="10">
+        <v>11600</v>
+      </c>
+      <c r="I15" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11992</v>
-      </c>
-      <c r="K14" s="10">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10">
-        <f t="shared" si="8"/>
-        <v>11992</v>
-      </c>
-      <c r="O14" s="10">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11992</v>
-      </c>
-      <c r="Q14" s="10">
-        <v>0</v>
-      </c>
-      <c r="R14" s="8"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10">
+      <c r="J15" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11600</v>
+      </c>
+      <c r="K15" s="10">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10">
+        <f t="shared" ref="N10:N58" si="14">IF((J15-K15)&lt;0,0,(J15-K15))</f>
+        <v>11600</v>
+      </c>
+      <c r="O15" s="10">
+        <f t="shared" ref="O10:O58" si="15">IF((K15-J15)&lt;0,0,(K15-J15))</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11600</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10">
         <f t="shared" si="10"/>
-        <v>11992</v>
-      </c>
-      <c r="U14" s="10">
+        <v>11600</v>
+      </c>
+      <c r="U15" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="V14" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11992</v>
-      </c>
-      <c r="W14" s="10">
-        <v>0</v>
-      </c>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="10"/>
-      <c r="Z14" s="10">
+      <c r="V15" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>11600</v>
+      </c>
+      <c r="W15" s="10">
+        <v>0</v>
+      </c>
+      <c r="X15" s="8"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10">
         <f t="shared" si="12"/>
-        <v>11992</v>
-      </c>
-      <c r="AA14" s="10">
+        <v>11600</v>
+      </c>
+      <c r="AA15" s="10">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" ht="15">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
-      <c r="Z15" s="5"/>
-      <c r="AA15" s="5"/>
     </row>
     <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="8">
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C16" s="8">
         <v>1450</v>
@@ -10765,11 +9894,11 @@
       <c r="L16" s="8"/>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
-        <f t="shared" ref="N11:N59" si="14">IF((J16-K16)&lt;0,0,(J16-K16))</f>
+        <f t="shared" si="14"/>
         <v>11600</v>
       </c>
       <c r="O16" s="10">
-        <f t="shared" ref="O11:O59" si="15">IF((K16-J16)&lt;0,0,(K16-J16))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="P16" s="10">
@@ -10812,7 +9941,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" s="8">
         <v>1450</v>
@@ -10891,7 +10020,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="8">
         <v>1450</v>
@@ -10965,12 +10094,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.5">
+    <row r="19" spans="1:27" s="5" customFormat="1" ht="19.5">
       <c r="A19" s="8">
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C19" s="8">
         <v>1450</v>
@@ -11044,12 +10173,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="5" customFormat="1" ht="19.5">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="8">
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C20" s="8">
         <v>1450</v>
@@ -11064,11 +10193,11 @@
       <c r="F20" s="8"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H20:H58" si="16">IF((D20-E20)&lt;0,0,(D20-E20))</f>
         <v>11600</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I20:I58" si="17">IF((E20-D20)&lt;0,0,(E20-D20))</f>
         <v>0</v>
       </c>
       <c r="J20" s="10">
@@ -11081,11 +10210,11 @@
       <c r="L20" s="8"/>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="N20:N25" si="18">IF((J20-K20)&lt;0,0,(J20-K20))</f>
         <v>11600</v>
       </c>
       <c r="O20" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="O20:O25" si="19">IF((K20-J20)&lt;0,0,(K20-J20))</f>
         <v>0</v>
       </c>
       <c r="P20" s="10">
@@ -11124,11 +10253,11 @@
       </c>
     </row>
     <row r="21" spans="1:27" ht="19.5">
-      <c r="A21" s="8">
+      <c r="A21" s="29">
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="C21" s="8">
         <v>1450</v>
@@ -11143,11 +10272,11 @@
       <c r="F21" s="8"/>
       <c r="G21" s="10"/>
       <c r="H21" s="10">
-        <f t="shared" ref="H21:H59" si="16">IF((D21-E21)&lt;0,0,(D21-E21))</f>
+        <f>IF((D21-E21)&lt;0,0,(D21-E21))</f>
         <v>11600</v>
       </c>
       <c r="I21" s="10">
-        <f t="shared" ref="I21:I59" si="17">IF((E21-D21)&lt;0,0,(E21-D21))</f>
+        <f>IF((E21-D21)&lt;0,0,(E21-D21))</f>
         <v>0</v>
       </c>
       <c r="J21" s="10">
@@ -11160,11 +10289,11 @@
       <c r="L21" s="8"/>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
-        <f t="shared" ref="N21:N26" si="18">IF((J21-K21)&lt;0,0,(J21-K21))</f>
+        <f t="shared" si="18"/>
         <v>11600</v>
       </c>
       <c r="O21" s="10">
-        <f t="shared" ref="O21:O26" si="19">IF((K21-J21)&lt;0,0,(K21-J21))</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="P21" s="10">
@@ -11177,11 +10306,11 @@
       <c r="R21" s="8"/>
       <c r="S21" s="10"/>
       <c r="T21" s="10">
-        <f t="shared" si="10"/>
+        <f>IF((P21-Q21)&lt;0,0,(P21-Q21))</f>
         <v>11600</v>
       </c>
       <c r="U21" s="10">
-        <f t="shared" si="11"/>
+        <f>IF((Q21-P21)&lt;0,0,(Q21-P21))</f>
         <v>0</v>
       </c>
       <c r="V21" s="10">
@@ -11194,20 +10323,20 @@
       <c r="X21" s="8"/>
       <c r="Y21" s="10"/>
       <c r="Z21" s="10">
-        <f t="shared" si="12"/>
+        <f>IF((V21-W21)&lt;0,0,(V21-W21))</f>
         <v>11600</v>
       </c>
       <c r="AA21" s="10">
-        <f t="shared" si="13"/>
+        <f>IF((W21-V21)&lt;0,0,(W21-V21))</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="19.5">
-      <c r="A22" s="32">
+      <c r="A22" s="8">
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C22" s="8">
         <v>1450</v>
@@ -11222,11 +10351,11 @@
       <c r="F22" s="8"/>
       <c r="G22" s="10"/>
       <c r="H22" s="10">
-        <f>IF((D22-E22)&lt;0,0,(D22-E22))</f>
+        <f t="shared" si="16"/>
         <v>11600</v>
       </c>
       <c r="I22" s="10">
-        <f>IF((E22-D22)&lt;0,0,(E22-D22))</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="J22" s="10">
@@ -11256,11 +10385,11 @@
       <c r="R22" s="8"/>
       <c r="S22" s="10"/>
       <c r="T22" s="10">
-        <f>IF((P22-Q22)&lt;0,0,(P22-Q22))</f>
+        <f t="shared" si="10"/>
         <v>11600</v>
       </c>
       <c r="U22" s="10">
-        <f>IF((Q22-P22)&lt;0,0,(Q22-P22))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V22" s="10">
@@ -11273,11 +10402,11 @@
       <c r="X22" s="8"/>
       <c r="Y22" s="10"/>
       <c r="Z22" s="10">
-        <f>IF((V22-W22)&lt;0,0,(V22-W22))</f>
+        <f t="shared" si="12"/>
         <v>11600</v>
       </c>
       <c r="AA22" s="10">
-        <f>IF((W22-V22)&lt;0,0,(W22-V22))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -11286,7 +10415,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="C23" s="8">
         <v>1450</v>
@@ -11361,11 +10490,11 @@
       </c>
     </row>
     <row r="24" spans="1:27" ht="19.5">
-      <c r="A24" s="8">
+      <c r="A24" s="29">
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C24" s="8">
         <v>1450</v>
@@ -11380,11 +10509,11 @@
       <c r="F24" s="8"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10">
-        <f t="shared" si="16"/>
+        <f>IF((D24-E24)&lt;0,0,(D24-E24))</f>
         <v>11600</v>
       </c>
       <c r="I24" s="10">
-        <f t="shared" si="17"/>
+        <f>IF((E24-D24)&lt;0,0,(E24-D24))</f>
         <v>0</v>
       </c>
       <c r="J24" s="10">
@@ -11414,11 +10543,11 @@
       <c r="R24" s="8"/>
       <c r="S24" s="10"/>
       <c r="T24" s="10">
-        <f t="shared" si="10"/>
+        <f>IF((P24-Q24)&lt;0,0,(P24-Q24))</f>
         <v>11600</v>
       </c>
       <c r="U24" s="10">
-        <f t="shared" si="11"/>
+        <f>IF((Q24-P24)&lt;0,0,(Q24-P24))</f>
         <v>0</v>
       </c>
       <c r="V24" s="10">
@@ -11431,20 +10560,20 @@
       <c r="X24" s="8"/>
       <c r="Y24" s="10"/>
       <c r="Z24" s="10">
-        <f t="shared" si="12"/>
+        <f>IF((V24-W24)&lt;0,0,(V24-W24))</f>
         <v>11600</v>
       </c>
       <c r="AA24" s="10">
-        <f t="shared" si="13"/>
+        <f>IF((W24-V24)&lt;0,0,(W24-V24))</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="19.5">
-      <c r="A25" s="32">
+      <c r="A25" s="8">
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" s="8">
         <v>1450</v>
@@ -11459,11 +10588,11 @@
       <c r="F25" s="8"/>
       <c r="G25" s="10"/>
       <c r="H25" s="10">
-        <f>IF((D25-E25)&lt;0,0,(D25-E25))</f>
+        <f t="shared" si="16"/>
         <v>11600</v>
       </c>
       <c r="I25" s="10">
-        <f>IF((E25-D25)&lt;0,0,(E25-D25))</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="J25" s="10">
@@ -11493,11 +10622,11 @@
       <c r="R25" s="8"/>
       <c r="S25" s="10"/>
       <c r="T25" s="10">
-        <f>IF((P25-Q25)&lt;0,0,(P25-Q25))</f>
+        <f t="shared" si="10"/>
         <v>11600</v>
       </c>
       <c r="U25" s="10">
-        <f>IF((Q25-P25)&lt;0,0,(Q25-P25))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V25" s="10">
@@ -11510,128 +10639,136 @@
       <c r="X25" s="8"/>
       <c r="Y25" s="10"/>
       <c r="Z25" s="10">
-        <f>IF((V25-W25)&lt;0,0,(V25-W25))</f>
+        <f t="shared" si="12"/>
         <v>11600</v>
       </c>
       <c r="AA25" s="10">
-        <f>IF((W25-V25)&lt;0,0,(W25-V25))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="19.5">
-      <c r="A26" s="8">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="15">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="5"/>
+      <c r="Y26" s="5"/>
+      <c r="Z26" s="5"/>
+      <c r="AA26" s="5"/>
+    </row>
+    <row r="27" spans="1:27" ht="19.5">
+      <c r="A27" s="8">
+        <v>9</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="8">
-        <v>1450</v>
-      </c>
-      <c r="D26" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11600</v>
-      </c>
-      <c r="E26" s="10">
-        <v>0</v>
-      </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10">
+      <c r="C27" s="8">
+        <v>1128</v>
+      </c>
+      <c r="D27" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9024</v>
+      </c>
+      <c r="E27" s="10">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10">
         <f t="shared" si="16"/>
-        <v>11600</v>
-      </c>
-      <c r="I26" s="10">
+        <v>9024</v>
+      </c>
+      <c r="I27" s="10">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="J26" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11600</v>
-      </c>
-      <c r="K26" s="10">
-        <v>0</v>
-      </c>
-      <c r="L26" s="8"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10">
-        <f t="shared" si="18"/>
-        <v>11600</v>
-      </c>
-      <c r="O26" s="10">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11600</v>
-      </c>
-      <c r="Q26" s="10">
-        <v>0</v>
-      </c>
-      <c r="R26" s="8"/>
-      <c r="S26" s="10"/>
-      <c r="T26" s="10">
+      <c r="J27" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9024</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0</v>
+      </c>
+      <c r="L27" s="8"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10">
+        <f t="shared" si="14"/>
+        <v>9024</v>
+      </c>
+      <c r="O27" s="10">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9024</v>
+      </c>
+      <c r="Q27" s="10">
+        <v>176</v>
+      </c>
+      <c r="R27" s="8">
+        <v>2025</v>
+      </c>
+      <c r="S27" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="T27" s="10">
         <f t="shared" si="10"/>
-        <v>11600</v>
-      </c>
-      <c r="U26" s="10">
+        <v>8848</v>
+      </c>
+      <c r="U27" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="V26" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>11600</v>
-      </c>
-      <c r="W26" s="10">
-        <v>0</v>
-      </c>
-      <c r="X26" s="8"/>
-      <c r="Y26" s="10"/>
-      <c r="Z26" s="10">
+      <c r="V27" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9024</v>
+      </c>
+      <c r="W27" s="10">
+        <v>176</v>
+      </c>
+      <c r="X27" s="8">
+        <v>2025</v>
+      </c>
+      <c r="Y27" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z27" s="10">
         <f t="shared" si="12"/>
-        <v>11600</v>
-      </c>
-      <c r="AA26" s="10">
+        <v>8848</v>
+      </c>
+      <c r="AA27" s="10">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:27" ht="15">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
-      <c r="U27" s="5"/>
-      <c r="V27" s="5"/>
-      <c r="W27" s="5"/>
-      <c r="X27" s="5"/>
-      <c r="Y27" s="5"/>
-      <c r="Z27" s="5"/>
-      <c r="AA27" s="5"/>
     </row>
     <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="8">
         <v>9</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C28" s="8">
         <v>1128</v>
@@ -11658,13 +10795,17 @@
         <v>9024</v>
       </c>
       <c r="K28" s="10">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8"/>
-      <c r="M28" s="10"/>
+        <v>187</v>
+      </c>
+      <c r="L28" s="8">
+        <v>2025</v>
+      </c>
+      <c r="M28" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="N28" s="10">
         <f t="shared" si="14"/>
-        <v>9024</v>
+        <v>8837</v>
       </c>
       <c r="O28" s="10">
         <f t="shared" si="15"/>
@@ -11675,17 +10816,13 @@
         <v>9024</v>
       </c>
       <c r="Q28" s="10">
-        <v>176</v>
-      </c>
-      <c r="R28" s="8">
-        <v>2025</v>
-      </c>
-      <c r="S28" s="10" t="s">
-        <v>56</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R28" s="8"/>
+      <c r="S28" s="10"/>
       <c r="T28" s="10">
         <f t="shared" si="10"/>
-        <v>8848</v>
+        <v>9024</v>
       </c>
       <c r="U28" s="10">
         <f t="shared" si="11"/>
@@ -11713,12 +10850,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.5">
+    <row r="29" spans="1:27" s="5" customFormat="1" ht="19.5">
       <c r="A29" s="8">
         <v>9</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="8">
         <v>1128</v>
@@ -11748,7 +10885,7 @@
         <v>187</v>
       </c>
       <c r="L29" s="8">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="M29" s="10" t="s">
         <v>56</v>
@@ -11800,12 +10937,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="5" customFormat="1" ht="19.5">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="8">
         <v>9</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30" s="8">
         <v>1128</v>
@@ -11832,17 +10969,13 @@
         <v>9024</v>
       </c>
       <c r="K30" s="10">
-        <v>187</v>
-      </c>
-      <c r="L30" s="8">
-        <v>2026</v>
-      </c>
-      <c r="M30" s="10" t="s">
-        <v>56</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L30" s="8"/>
+      <c r="M30" s="10"/>
       <c r="N30" s="10">
         <f t="shared" si="14"/>
-        <v>8837</v>
+        <v>9024</v>
       </c>
       <c r="O30" s="10">
         <f t="shared" si="15"/>
@@ -11853,13 +10986,17 @@
         <v>9024</v>
       </c>
       <c r="Q30" s="10">
-        <v>0</v>
-      </c>
-      <c r="R30" s="8"/>
-      <c r="S30" s="10"/>
+        <v>176</v>
+      </c>
+      <c r="R30" s="8">
+        <v>2025</v>
+      </c>
+      <c r="S30" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="T30" s="10">
         <f t="shared" si="10"/>
-        <v>9024</v>
+        <v>8848</v>
       </c>
       <c r="U30" s="10">
         <f t="shared" si="11"/>
@@ -11892,7 +11029,7 @@
         <v>9</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C31" s="8">
         <v>1128</v>
@@ -11979,7 +11116,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C32" s="8">
         <v>1128</v>
@@ -12062,11 +11199,11 @@
       </c>
     </row>
     <row r="33" spans="1:27" ht="19.5">
-      <c r="A33" s="8">
+      <c r="A33" s="29">
         <v>9</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="C33" s="8">
         <v>1128</v>
@@ -12081,11 +11218,11 @@
       <c r="F33" s="8"/>
       <c r="G33" s="10"/>
       <c r="H33" s="10">
-        <f t="shared" si="16"/>
+        <f>IF((D33-E33)&lt;0,0,(D33-E33))</f>
         <v>9024</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="17"/>
+        <f>IF((E33-D33)&lt;0,0,(E33-D33))</f>
         <v>0</v>
       </c>
       <c r="J33" s="10">
@@ -12098,11 +11235,11 @@
       <c r="L33" s="8"/>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="N33:N37" si="20">IF((J33-K33)&lt;0,0,(J33-K33))</f>
         <v>9024</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="O33:O37" si="21">IF((K33-J33)&lt;0,0,(K33-J33))</f>
         <v>0</v>
       </c>
       <c r="P33" s="10">
@@ -12110,20 +11247,16 @@
         <v>9024</v>
       </c>
       <c r="Q33" s="10">
-        <v>176</v>
-      </c>
-      <c r="R33" s="8">
-        <v>2025</v>
-      </c>
-      <c r="S33" s="10" t="s">
-        <v>56</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R33" s="8"/>
+      <c r="S33" s="10"/>
       <c r="T33" s="10">
-        <f t="shared" si="10"/>
-        <v>8848</v>
+        <f>IF((P33-Q33)&lt;0,0,(P33-Q33))</f>
+        <v>9024</v>
       </c>
       <c r="U33" s="10">
-        <f t="shared" si="11"/>
+        <f>IF((Q33-P33)&lt;0,0,(Q33-P33))</f>
         <v>0</v>
       </c>
       <c r="V33" s="10">
@@ -12140,20 +11273,20 @@
         <v>56</v>
       </c>
       <c r="Z33" s="10">
-        <f t="shared" si="12"/>
+        <f>IF((V33-W33)&lt;0,0,(V33-W33))</f>
         <v>8848</v>
       </c>
       <c r="AA33" s="10">
-        <f t="shared" si="13"/>
+        <f>IF((W33-V33)&lt;0,0,(W33-V33))</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:27" ht="19.5">
-      <c r="A34" s="32">
+      <c r="A34" s="8">
         <v>9</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="8">
         <v>1128</v>
@@ -12168,11 +11301,11 @@
       <c r="F34" s="8"/>
       <c r="G34" s="10"/>
       <c r="H34" s="10">
-        <f>IF((D34-E34)&lt;0,0,(D34-E34))</f>
+        <f t="shared" si="16"/>
         <v>9024</v>
       </c>
       <c r="I34" s="10">
-        <f>IF((E34-D34)&lt;0,0,(E34-D34))</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="J34" s="10">
@@ -12185,11 +11318,11 @@
       <c r="L34" s="8"/>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
-        <f t="shared" ref="N34:N38" si="20">IF((J34-K34)&lt;0,0,(J34-K34))</f>
+        <f t="shared" si="20"/>
         <v>9024</v>
       </c>
       <c r="O34" s="10">
-        <f t="shared" ref="O34:O38" si="21">IF((K34-J34)&lt;0,0,(K34-J34))</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="P34" s="10">
@@ -12202,11 +11335,11 @@
       <c r="R34" s="8"/>
       <c r="S34" s="10"/>
       <c r="T34" s="10">
-        <f>IF((P34-Q34)&lt;0,0,(P34-Q34))</f>
+        <f t="shared" si="10"/>
         <v>9024</v>
       </c>
       <c r="U34" s="10">
-        <f>IF((Q34-P34)&lt;0,0,(Q34-P34))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V34" s="10">
@@ -12223,11 +11356,11 @@
         <v>56</v>
       </c>
       <c r="Z34" s="10">
-        <f>IF((V34-W34)&lt;0,0,(V34-W34))</f>
+        <f t="shared" si="12"/>
         <v>8848</v>
       </c>
       <c r="AA34" s="10">
-        <f>IF((W34-V34)&lt;0,0,(W34-V34))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -12236,7 +11369,7 @@
         <v>9</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="C35" s="8">
         <v>1128</v>
@@ -12297,17 +11430,13 @@
         <v>9024</v>
       </c>
       <c r="W35" s="10">
-        <v>176</v>
-      </c>
-      <c r="X35" s="8">
-        <v>2025</v>
-      </c>
-      <c r="Y35" s="10" t="s">
-        <v>56</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X35" s="8"/>
+      <c r="Y35" s="10"/>
       <c r="Z35" s="10">
         <f t="shared" si="12"/>
-        <v>8848</v>
+        <v>9024</v>
       </c>
       <c r="AA35" s="10">
         <f t="shared" si="13"/>
@@ -12315,11 +11444,11 @@
       </c>
     </row>
     <row r="36" spans="1:27" ht="19.5">
-      <c r="A36" s="8">
+      <c r="A36" s="29">
         <v>9</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C36" s="8">
         <v>1128</v>
@@ -12334,11 +11463,11 @@
       <c r="F36" s="8"/>
       <c r="G36" s="10"/>
       <c r="H36" s="10">
-        <f t="shared" si="16"/>
+        <f>IF((D36-E36)&lt;0,0,(D36-E36))</f>
         <v>9024</v>
       </c>
       <c r="I36" s="10">
-        <f t="shared" si="17"/>
+        <f>IF((E36-D36)&lt;0,0,(E36-D36))</f>
         <v>0</v>
       </c>
       <c r="J36" s="10">
@@ -12363,16 +11492,20 @@
         <v>9024</v>
       </c>
       <c r="Q36" s="10">
-        <v>0</v>
-      </c>
-      <c r="R36" s="8"/>
-      <c r="S36" s="10"/>
+        <v>176</v>
+      </c>
+      <c r="R36" s="8">
+        <v>2025</v>
+      </c>
+      <c r="S36" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="T36" s="10">
-        <f t="shared" si="10"/>
-        <v>9024</v>
+        <f>IF((P36-Q36)&lt;0,0,(P36-Q36))</f>
+        <v>8848</v>
       </c>
       <c r="U36" s="10">
-        <f t="shared" si="11"/>
+        <f>IF((Q36-P36)&lt;0,0,(Q36-P36))</f>
         <v>0</v>
       </c>
       <c r="V36" s="10">
@@ -12380,25 +11513,29 @@
         <v>9024</v>
       </c>
       <c r="W36" s="10">
-        <v>0</v>
-      </c>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="10"/>
+        <v>176</v>
+      </c>
+      <c r="X36" s="8">
+        <v>2025</v>
+      </c>
+      <c r="Y36" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="Z36" s="10">
-        <f t="shared" si="12"/>
-        <v>9024</v>
+        <f>IF((V36-W36)&lt;0,0,(V36-W36))</f>
+        <v>8848</v>
       </c>
       <c r="AA36" s="10">
-        <f t="shared" si="13"/>
+        <f>IF((W36-V36)&lt;0,0,(W36-V36))</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="19.5">
-      <c r="A37" s="32">
+      <c r="A37" s="8">
         <v>9</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C37" s="8">
         <v>1128</v>
@@ -12413,11 +11550,11 @@
       <c r="F37" s="8"/>
       <c r="G37" s="10"/>
       <c r="H37" s="10">
-        <f>IF((D37-E37)&lt;0,0,(D37-E37))</f>
+        <f t="shared" si="16"/>
         <v>9024</v>
       </c>
       <c r="I37" s="10">
-        <f>IF((E37-D37)&lt;0,0,(E37-D37))</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="J37" s="10">
@@ -12451,11 +11588,11 @@
         <v>56</v>
       </c>
       <c r="T37" s="10">
-        <f>IF((P37-Q37)&lt;0,0,(P37-Q37))</f>
+        <f t="shared" si="10"/>
         <v>8848</v>
       </c>
       <c r="U37" s="10">
-        <f>IF((Q37-P37)&lt;0,0,(Q37-P37))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V37" s="10">
@@ -12472,136 +11609,140 @@
         <v>56</v>
       </c>
       <c r="Z37" s="10">
-        <f>IF((V37-W37)&lt;0,0,(V37-W37))</f>
-        <v>8848</v>
-      </c>
-      <c r="AA37" s="10">
-        <f>IF((W37-V37)&lt;0,0,(W37-V37))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" ht="19.5">
-      <c r="A38" s="8">
-        <v>9</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="8">
-        <v>1128</v>
-      </c>
-      <c r="D38" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9024</v>
-      </c>
-      <c r="E38" s="10">
-        <v>0</v>
-      </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10">
-        <f t="shared" si="16"/>
-        <v>9024</v>
-      </c>
-      <c r="I38" s="10">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="J38" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9024</v>
-      </c>
-      <c r="K38" s="10">
-        <v>0</v>
-      </c>
-      <c r="L38" s="8"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10">
-        <f t="shared" si="20"/>
-        <v>9024</v>
-      </c>
-      <c r="O38" s="10">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="P38" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9024</v>
-      </c>
-      <c r="Q38" s="10">
-        <v>176</v>
-      </c>
-      <c r="R38" s="8">
-        <v>2025</v>
-      </c>
-      <c r="S38" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="T38" s="10">
-        <f t="shared" si="10"/>
-        <v>8848</v>
-      </c>
-      <c r="U38" s="10">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V38" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9024</v>
-      </c>
-      <c r="W38" s="10">
-        <v>176</v>
-      </c>
-      <c r="X38" s="8">
-        <v>2025</v>
-      </c>
-      <c r="Y38" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z38" s="10">
         <f t="shared" si="12"/>
         <v>8848</v>
       </c>
-      <c r="AA38" s="10">
+      <c r="AA37" s="10">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="15">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
-      <c r="S39" s="5"/>
-      <c r="T39" s="5"/>
-      <c r="U39" s="5"/>
-      <c r="V39" s="5"/>
-      <c r="W39" s="5"/>
-      <c r="X39" s="5"/>
-      <c r="Y39" s="5"/>
-      <c r="Z39" s="5"/>
-      <c r="AA39" s="5"/>
+    <row r="38" spans="1:27" ht="15">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+      <c r="W38" s="5"/>
+      <c r="X38" s="5"/>
+      <c r="Y38" s="5"/>
+      <c r="Z38" s="5"/>
+      <c r="AA38" s="5"/>
+    </row>
+    <row r="39" spans="1:27" ht="19.5">
+      <c r="A39" s="8">
+        <v>10</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="8">
+        <v>1222</v>
+      </c>
+      <c r="D39" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9776</v>
+      </c>
+      <c r="E39" s="10">
+        <v>0</v>
+      </c>
+      <c r="F39" s="8"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10">
+        <f t="shared" si="16"/>
+        <v>9776</v>
+      </c>
+      <c r="I39" s="10">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9776</v>
+      </c>
+      <c r="K39" s="10">
+        <v>250</v>
+      </c>
+      <c r="L39" s="8">
+        <v>2025</v>
+      </c>
+      <c r="M39" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="N39" s="10">
+        <f t="shared" si="14"/>
+        <v>9526</v>
+      </c>
+      <c r="O39" s="10">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="P39" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9776</v>
+      </c>
+      <c r="Q39" s="10">
+        <v>250</v>
+      </c>
+      <c r="R39" s="8">
+        <v>2025</v>
+      </c>
+      <c r="S39" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="T39" s="10">
+        <f t="shared" si="10"/>
+        <v>9526</v>
+      </c>
+      <c r="U39" s="10">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V39" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9776</v>
+      </c>
+      <c r="W39" s="10">
+        <v>250</v>
+      </c>
+      <c r="X39" s="8">
+        <v>2025</v>
+      </c>
+      <c r="Y39" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z39" s="10">
+        <f t="shared" si="12"/>
+        <v>9526</v>
+      </c>
+      <c r="AA39" s="10">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="8">
         <v>10</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C40" s="8">
         <v>1222</v>
@@ -12628,13 +11769,13 @@
         <v>9776</v>
       </c>
       <c r="K40" s="10">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L40" s="8"/>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
         <f t="shared" si="14"/>
-        <v>9526</v>
+        <v>9776</v>
       </c>
       <c r="O40" s="10">
         <f t="shared" si="15"/>
@@ -12683,12 +11824,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" s="5" customFormat="1" ht="19.5">
       <c r="A41" s="8">
         <v>10</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C41" s="8">
         <v>1222</v>
@@ -12698,13 +11839,17 @@
         <v>9776</v>
       </c>
       <c r="E41" s="10">
-        <v>0</v>
-      </c>
-      <c r="F41" s="8"/>
-      <c r="G41" s="10"/>
+        <v>476</v>
+      </c>
+      <c r="F41" s="8">
+        <v>2025</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="H41" s="10">
         <f t="shared" si="16"/>
-        <v>9776</v>
+        <v>9300</v>
       </c>
       <c r="I41" s="10">
         <f t="shared" si="17"/>
@@ -12715,13 +11860,17 @@
         <v>9776</v>
       </c>
       <c r="K41" s="10">
-        <v>0</v>
-      </c>
-      <c r="L41" s="8"/>
-      <c r="M41" s="10"/>
+        <v>250</v>
+      </c>
+      <c r="L41" s="8">
+        <v>2025</v>
+      </c>
+      <c r="M41" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="N41" s="10">
         <f t="shared" si="14"/>
-        <v>9776</v>
+        <v>9526</v>
       </c>
       <c r="O41" s="10">
         <f t="shared" si="15"/>
@@ -12770,12 +11919,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="5" customFormat="1" ht="19.5">
+    <row r="42" spans="1:27" ht="19.5">
       <c r="A42" s="8">
         <v>10</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C42" s="8">
         <v>1222</v>
@@ -12785,13 +11934,13 @@
         <v>9776</v>
       </c>
       <c r="E42" s="10">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="F42" s="8"/>
       <c r="G42" s="10"/>
       <c r="H42" s="10">
         <f t="shared" si="16"/>
-        <v>9300</v>
+        <v>9776</v>
       </c>
       <c r="I42" s="10">
         <f t="shared" si="17"/>
@@ -12802,13 +11951,13 @@
         <v>9776</v>
       </c>
       <c r="K42" s="10">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L42" s="8"/>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
         <f t="shared" si="14"/>
-        <v>9526</v>
+        <v>9776</v>
       </c>
       <c r="O42" s="10">
         <f t="shared" si="15"/>
@@ -12862,7 +12011,7 @@
         <v>10</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C43" s="8">
         <v>1222</v>
@@ -12949,7 +12098,7 @@
         <v>10</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C44" s="8">
         <v>1222</v>
@@ -13032,11 +12181,11 @@
       </c>
     </row>
     <row r="45" spans="1:27" ht="19.5">
-      <c r="A45" s="8">
+      <c r="A45" s="29">
         <v>10</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="C45" s="8">
         <v>1222</v>
@@ -13051,11 +12200,11 @@
       <c r="F45" s="8"/>
       <c r="G45" s="10"/>
       <c r="H45" s="10">
-        <f t="shared" si="16"/>
+        <f>IF((D45-E45)&lt;0,0,(D45-E45))</f>
         <v>9776</v>
       </c>
       <c r="I45" s="10">
-        <f t="shared" si="17"/>
+        <f>IF((E45-D45)&lt;0,0,(E45-D45))</f>
         <v>0</v>
       </c>
       <c r="J45" s="10">
@@ -13068,11 +12217,11 @@
       <c r="L45" s="8"/>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="N45:N49" si="22">IF((J45-K45)&lt;0,0,(J45-K45))</f>
         <v>9776</v>
       </c>
       <c r="O45" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="O45:O49" si="23">IF((K45-J45)&lt;0,0,(K45-J45))</f>
         <v>0</v>
       </c>
       <c r="P45" s="10">
@@ -13089,11 +12238,11 @@
         <v>56</v>
       </c>
       <c r="T45" s="10">
-        <f t="shared" si="10"/>
+        <f>IF((P45-Q45)&lt;0,0,(P45-Q45))</f>
         <v>9526</v>
       </c>
       <c r="U45" s="10">
-        <f t="shared" si="11"/>
+        <f>IF((Q45-P45)&lt;0,0,(Q45-P45))</f>
         <v>0</v>
       </c>
       <c r="V45" s="10">
@@ -13110,20 +12259,20 @@
         <v>56</v>
       </c>
       <c r="Z45" s="10">
-        <f t="shared" si="12"/>
+        <f>IF((V45-W45)&lt;0,0,(V45-W45))</f>
         <v>9526</v>
       </c>
       <c r="AA45" s="10">
-        <f t="shared" si="13"/>
+        <f>IF((W45-V45)&lt;0,0,(W45-V45))</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:27" ht="19.5">
-      <c r="A46" s="32">
+      <c r="A46" s="8">
         <v>10</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C46" s="8">
         <v>1222</v>
@@ -13138,11 +12287,11 @@
       <c r="F46" s="8"/>
       <c r="G46" s="10"/>
       <c r="H46" s="10">
-        <f>IF((D46-E46)&lt;0,0,(D46-E46))</f>
+        <f t="shared" si="16"/>
         <v>9776</v>
       </c>
       <c r="I46" s="10">
-        <f>IF((E46-D46)&lt;0,0,(E46-D46))</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="J46" s="10">
@@ -13155,11 +12304,11 @@
       <c r="L46" s="8"/>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
-        <f t="shared" ref="N46:N50" si="22">IF((J46-K46)&lt;0,0,(J46-K46))</f>
+        <f t="shared" si="22"/>
         <v>9776</v>
       </c>
       <c r="O46" s="10">
-        <f t="shared" ref="O46:O50" si="23">IF((K46-J46)&lt;0,0,(K46-J46))</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="P46" s="10">
@@ -13167,20 +12316,16 @@
         <v>9776</v>
       </c>
       <c r="Q46" s="10">
-        <v>250</v>
-      </c>
-      <c r="R46" s="8">
-        <v>2025</v>
-      </c>
-      <c r="S46" s="10" t="s">
-        <v>56</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R46" s="8"/>
+      <c r="S46" s="10"/>
       <c r="T46" s="10">
-        <f>IF((P46-Q46)&lt;0,0,(P46-Q46))</f>
-        <v>9526</v>
+        <f t="shared" si="10"/>
+        <v>9776</v>
       </c>
       <c r="U46" s="10">
-        <f>IF((Q46-P46)&lt;0,0,(Q46-P46))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V46" s="10">
@@ -13197,11 +12342,11 @@
         <v>56</v>
       </c>
       <c r="Z46" s="10">
-        <f>IF((V46-W46)&lt;0,0,(V46-W46))</f>
+        <f t="shared" si="12"/>
         <v>9526</v>
       </c>
       <c r="AA46" s="10">
-        <f>IF((W46-V46)&lt;0,0,(W46-V46))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
@@ -13210,7 +12355,7 @@
         <v>10</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="C47" s="8">
         <v>1222</v>
@@ -13271,17 +12416,13 @@
         <v>9776</v>
       </c>
       <c r="W47" s="10">
-        <v>250</v>
-      </c>
-      <c r="X47" s="8">
-        <v>2025</v>
-      </c>
-      <c r="Y47" s="10" t="s">
-        <v>56</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X47" s="8"/>
+      <c r="Y47" s="10"/>
       <c r="Z47" s="10">
         <f t="shared" si="12"/>
-        <v>9526</v>
+        <v>9776</v>
       </c>
       <c r="AA47" s="10">
         <f t="shared" si="13"/>
@@ -13289,11 +12430,11 @@
       </c>
     </row>
     <row r="48" spans="1:27" ht="19.5">
-      <c r="A48" s="8">
+      <c r="A48" s="29">
         <v>10</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C48" s="8">
         <v>1222</v>
@@ -13308,11 +12449,11 @@
       <c r="F48" s="8"/>
       <c r="G48" s="10"/>
       <c r="H48" s="10">
-        <f t="shared" si="16"/>
+        <f>IF((D48-E48)&lt;0,0,(D48-E48))</f>
         <v>9776</v>
       </c>
       <c r="I48" s="10">
-        <f t="shared" si="17"/>
+        <f>IF((E48-D48)&lt;0,0,(E48-D48))</f>
         <v>0</v>
       </c>
       <c r="J48" s="10">
@@ -13337,16 +12478,20 @@
         <v>9776</v>
       </c>
       <c r="Q48" s="10">
-        <v>0</v>
-      </c>
-      <c r="R48" s="8"/>
-      <c r="S48" s="10"/>
+        <v>250</v>
+      </c>
+      <c r="R48" s="8">
+        <v>2025</v>
+      </c>
+      <c r="S48" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="T48" s="10">
-        <f t="shared" si="10"/>
-        <v>9776</v>
+        <f>IF((P48-Q48)&lt;0,0,(P48-Q48))</f>
+        <v>9526</v>
       </c>
       <c r="U48" s="10">
-        <f t="shared" si="11"/>
+        <f>IF((Q48-P48)&lt;0,0,(Q48-P48))</f>
         <v>0</v>
       </c>
       <c r="V48" s="10">
@@ -13359,20 +12504,20 @@
       <c r="X48" s="8"/>
       <c r="Y48" s="10"/>
       <c r="Z48" s="10">
-        <f t="shared" si="12"/>
+        <f>IF((V48-W48)&lt;0,0,(V48-W48))</f>
         <v>9776</v>
       </c>
       <c r="AA48" s="10">
-        <f t="shared" si="13"/>
+        <f>IF((W48-V48)&lt;0,0,(W48-V48))</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:27" ht="19.5">
-      <c r="A49" s="32">
+      <c r="A49" s="8">
         <v>10</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C49" s="8">
         <v>1222</v>
@@ -13387,11 +12532,11 @@
       <c r="F49" s="8"/>
       <c r="G49" s="10"/>
       <c r="H49" s="10">
-        <f>IF((D49-E49)&lt;0,0,(D49-E49))</f>
+        <f t="shared" si="16"/>
         <v>9776</v>
       </c>
       <c r="I49" s="10">
-        <f>IF((E49-D49)&lt;0,0,(E49-D49))</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="J49" s="10">
@@ -13425,165 +12570,165 @@
         <v>56</v>
       </c>
       <c r="T49" s="10">
-        <f>IF((P49-Q49)&lt;0,0,(P49-Q49))</f>
-        <v>9526</v>
-      </c>
-      <c r="U49" s="10">
-        <f>IF((Q49-P49)&lt;0,0,(Q49-P49))</f>
-        <v>0</v>
-      </c>
-      <c r="V49" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9776</v>
-      </c>
-      <c r="W49" s="10">
-        <v>0</v>
-      </c>
-      <c r="X49" s="8"/>
-      <c r="Y49" s="10"/>
-      <c r="Z49" s="10">
-        <f>IF((V49-W49)&lt;0,0,(V49-W49))</f>
-        <v>9776</v>
-      </c>
-      <c r="AA49" s="10">
-        <f>IF((W49-V49)&lt;0,0,(W49-V49))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:27" ht="19.5">
-      <c r="A50" s="8">
-        <v>10</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C50" s="8">
-        <v>1222</v>
-      </c>
-      <c r="D50" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9776</v>
-      </c>
-      <c r="E50" s="10">
-        <v>0</v>
-      </c>
-      <c r="F50" s="8"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10">
-        <f t="shared" si="16"/>
-        <v>9776</v>
-      </c>
-      <c r="I50" s="10">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="J50" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9776</v>
-      </c>
-      <c r="K50" s="10">
-        <v>0</v>
-      </c>
-      <c r="L50" s="8"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="10">
-        <f t="shared" si="22"/>
-        <v>9776</v>
-      </c>
-      <c r="O50" s="10">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="P50" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9776</v>
-      </c>
-      <c r="Q50" s="10">
-        <v>250</v>
-      </c>
-      <c r="R50" s="8">
-        <v>2025</v>
-      </c>
-      <c r="S50" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="T50" s="10">
         <f t="shared" si="10"/>
         <v>9526</v>
       </c>
-      <c r="U50" s="10">
+      <c r="U49" s="10">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="V50" s="10">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>9776</v>
-      </c>
-      <c r="W50" s="10">
+      <c r="V49" s="10">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>9776</v>
+      </c>
+      <c r="W49" s="10">
         <v>250</v>
       </c>
-      <c r="X50" s="8">
+      <c r="X49" s="8">
         <v>2025</v>
       </c>
-      <c r="Y50" s="10" t="s">
+      <c r="Y49" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="Z50" s="10">
+      <c r="Z49" s="10">
         <f t="shared" si="12"/>
         <v>9526</v>
       </c>
-      <c r="AA50" s="10">
+      <c r="AA49" s="10">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="15">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="5"/>
-      <c r="R51" s="5"/>
-      <c r="S51" s="5"/>
-      <c r="T51" s="5"/>
-      <c r="U51" s="5"/>
-      <c r="V51" s="5"/>
-      <c r="W51" s="5"/>
-      <c r="X51" s="5"/>
-      <c r="Y51" s="5"/>
-      <c r="Z51" s="5"/>
-      <c r="AA51" s="5"/>
-    </row>
-    <row r="52" spans="1:27" ht="38.25">
+    <row r="50" spans="1:27" ht="15">
+      <c r="A50" s="5"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
+      <c r="R50" s="5"/>
+      <c r="S50" s="5"/>
+      <c r="T50" s="5"/>
+      <c r="U50" s="5"/>
+      <c r="V50" s="5"/>
+      <c r="W50" s="5"/>
+      <c r="X50" s="5"/>
+      <c r="Y50" s="5"/>
+      <c r="Z50" s="5"/>
+      <c r="AA50" s="5"/>
+    </row>
+    <row r="51" spans="1:27" ht="38.25">
+      <c r="A51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="1">
+        <v>822</v>
+      </c>
+      <c r="D51" s="4">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>6576</v>
+      </c>
+      <c r="E51" s="4">
+        <v>0</v>
+      </c>
+      <c r="F51" s="1"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4">
+        <f t="shared" si="16"/>
+        <v>6576</v>
+      </c>
+      <c r="I51" s="4">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="4">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>6576</v>
+      </c>
+      <c r="K51" s="4">
+        <v>0</v>
+      </c>
+      <c r="L51" s="1"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4">
+        <f t="shared" si="14"/>
+        <v>6576</v>
+      </c>
+      <c r="O51" s="4">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="P51" s="4">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>6576</v>
+      </c>
+      <c r="Q51" s="4">
+        <v>0</v>
+      </c>
+      <c r="R51" s="1"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="4">
+        <f t="shared" si="10"/>
+        <v>6576</v>
+      </c>
+      <c r="U51" s="4">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="4">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>6576</v>
+      </c>
+      <c r="W51" s="4">
+        <v>0</v>
+      </c>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="4">
+        <f t="shared" si="12"/>
+        <v>6576</v>
+      </c>
+      <c r="AA51" s="4">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="C52" s="1">
+        <v>822</v>
+      </c>
       <c r="D52" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E52" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="E52" s="4">
+        <v>0</v>
+      </c>
       <c r="F52" s="1"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="I52" s="4">
         <f t="shared" si="17"/>
@@ -13591,14 +12736,16 @@
       </c>
       <c r="J52" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K52" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="K52" s="4">
+        <v>0</v>
+      </c>
       <c r="L52" s="1"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="O52" s="4">
         <f t="shared" si="15"/>
@@ -13606,14 +12753,16 @@
       </c>
       <c r="P52" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q52" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="Q52" s="4">
+        <v>0</v>
+      </c>
       <c r="R52" s="1"/>
       <c r="S52" s="4"/>
       <c r="T52" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="U52" s="4">
         <f t="shared" si="11"/>
@@ -13621,38 +12770,44 @@
       </c>
       <c r="V52" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W52" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="W52" s="4">
+        <v>0</v>
+      </c>
       <c r="X52" s="1"/>
       <c r="Y52" s="4"/>
       <c r="Z52" s="4">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="AA52" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.5">
+    <row r="53" spans="1:27" s="5" customFormat="1" ht="19.5">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C53" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="C53" s="1">
+        <v>822</v>
+      </c>
       <c r="D53" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E53" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="E53" s="4">
+        <v>0</v>
+      </c>
       <c r="F53" s="1"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="I53" s="4">
         <f t="shared" si="17"/>
@@ -13660,14 +12815,16 @@
       </c>
       <c r="J53" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K53" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="K53" s="4">
+        <v>0</v>
+      </c>
       <c r="L53" s="1"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="O53" s="4">
         <f t="shared" si="15"/>
@@ -13675,14 +12832,16 @@
       </c>
       <c r="P53" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q53" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="Q53" s="4">
+        <v>0</v>
+      </c>
       <c r="R53" s="1"/>
       <c r="S53" s="4"/>
       <c r="T53" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="U53" s="4">
         <f t="shared" si="11"/>
@@ -13690,38 +12849,44 @@
       </c>
       <c r="V53" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W53" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="W53" s="4">
+        <v>0</v>
+      </c>
       <c r="X53" s="1"/>
       <c r="Y53" s="4"/>
       <c r="Z53" s="4">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="AA53" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="5" customFormat="1" ht="19.5">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C54" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="C54" s="1">
+        <v>822</v>
+      </c>
       <c r="D54" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E54" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="E54" s="4">
+        <v>0</v>
+      </c>
       <c r="F54" s="1"/>
       <c r="G54" s="4"/>
       <c r="H54" s="4">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="I54" s="4">
         <f t="shared" si="17"/>
@@ -13729,14 +12894,16 @@
       </c>
       <c r="J54" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K54" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="K54" s="4">
+        <v>0</v>
+      </c>
       <c r="L54" s="1"/>
       <c r="M54" s="4"/>
       <c r="N54" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="O54" s="4">
         <f t="shared" si="15"/>
@@ -13744,14 +12911,16 @@
       </c>
       <c r="P54" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q54" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="Q54" s="4">
+        <v>0</v>
+      </c>
       <c r="R54" s="1"/>
       <c r="S54" s="4"/>
       <c r="T54" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="U54" s="4">
         <f t="shared" si="11"/>
@@ -13759,38 +12928,44 @@
       </c>
       <c r="V54" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W54" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="W54" s="4">
+        <v>0</v>
+      </c>
       <c r="X54" s="1"/>
       <c r="Y54" s="4"/>
       <c r="Z54" s="4">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="AA54" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.5">
+    <row r="55" spans="1:27" ht="38.25">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C55" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="C55" s="1">
+        <v>822</v>
+      </c>
       <c r="D55" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E55" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="E55" s="4">
+        <v>0</v>
+      </c>
       <c r="F55" s="1"/>
       <c r="G55" s="4"/>
       <c r="H55" s="4">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="I55" s="4">
         <f t="shared" si="17"/>
@@ -13798,14 +12973,16 @@
       </c>
       <c r="J55" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K55" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="K55" s="4">
+        <v>0</v>
+      </c>
       <c r="L55" s="1"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="O55" s="4">
         <f t="shared" si="15"/>
@@ -13813,14 +12990,16 @@
       </c>
       <c r="P55" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q55" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="Q55" s="4">
+        <v>0</v>
+      </c>
       <c r="R55" s="1"/>
       <c r="S55" s="4"/>
       <c r="T55" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="U55" s="4">
         <f t="shared" si="11"/>
@@ -13828,14 +13007,16 @@
       </c>
       <c r="V55" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W55" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="W55" s="4">
+        <v>0</v>
+      </c>
       <c r="X55" s="1"/>
       <c r="Y55" s="4"/>
       <c r="Z55" s="4">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="AA55" s="4">
         <f t="shared" si="13"/>
@@ -13847,19 +13028,23 @@
         <v>19</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="C56" s="1">
+        <v>822</v>
+      </c>
       <c r="D56" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E56" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="E56" s="4">
+        <v>0</v>
+      </c>
       <c r="F56" s="1"/>
       <c r="G56" s="4"/>
       <c r="H56" s="4">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="I56" s="4">
         <f t="shared" si="17"/>
@@ -13867,14 +13052,16 @@
       </c>
       <c r="J56" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K56" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="K56" s="4">
+        <v>0</v>
+      </c>
       <c r="L56" s="1"/>
       <c r="M56" s="4"/>
       <c r="N56" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="O56" s="4">
         <f t="shared" si="15"/>
@@ -13882,14 +13069,16 @@
       </c>
       <c r="P56" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q56" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="Q56" s="4">
+        <v>0</v>
+      </c>
       <c r="R56" s="1"/>
       <c r="S56" s="4"/>
       <c r="T56" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="U56" s="4">
         <f t="shared" si="11"/>
@@ -13897,38 +13086,44 @@
       </c>
       <c r="V56" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W56" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="W56" s="4">
+        <v>0</v>
+      </c>
       <c r="X56" s="1"/>
       <c r="Y56" s="4"/>
       <c r="Z56" s="4">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="AA56" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="38.25">
+    <row r="57" spans="1:27" ht="57.75">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C57" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="C57" s="1">
+        <v>822</v>
+      </c>
       <c r="D57" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E57" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="E57" s="4">
+        <v>0</v>
+      </c>
       <c r="F57" s="1"/>
       <c r="G57" s="4"/>
       <c r="H57" s="4">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="I57" s="4">
         <f t="shared" si="17"/>
@@ -13936,14 +13131,16 @@
       </c>
       <c r="J57" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K57" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="K57" s="4">
+        <v>0</v>
+      </c>
       <c r="L57" s="1"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="O57" s="4">
         <f t="shared" si="15"/>
@@ -13951,14 +13148,16 @@
       </c>
       <c r="P57" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q57" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="Q57" s="4">
+        <v>0</v>
+      </c>
       <c r="R57" s="1"/>
       <c r="S57" s="4"/>
       <c r="T57" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="U57" s="4">
         <f t="shared" si="11"/>
@@ -13966,38 +13165,44 @@
       </c>
       <c r="V57" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W57" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="W57" s="4">
+        <v>0</v>
+      </c>
       <c r="X57" s="1"/>
       <c r="Y57" s="4"/>
       <c r="Z57" s="4">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="AA57" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="57.75">
+    <row r="58" spans="1:27" ht="38.25">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C58" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="C58" s="1">
+        <v>822</v>
+      </c>
       <c r="D58" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E58" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="E58" s="4">
+        <v>0</v>
+      </c>
       <c r="F58" s="1"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="I58" s="4">
         <f t="shared" si="17"/>
@@ -14005,14 +13210,16 @@
       </c>
       <c r="J58" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K58" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="K58" s="4">
+        <v>0</v>
+      </c>
       <c r="L58" s="1"/>
       <c r="M58" s="4"/>
       <c r="N58" s="4">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="O58" s="4">
         <f t="shared" si="15"/>
@@ -14020,14 +13227,16 @@
       </c>
       <c r="P58" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="Q58" s="4">
+        <v>0</v>
+      </c>
       <c r="R58" s="1"/>
       <c r="S58" s="4"/>
       <c r="T58" s="4">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="U58" s="4">
         <f t="shared" si="11"/>
@@ -14035,612 +13244,98 @@
       </c>
       <c r="V58" s="4">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W58" s="4"/>
+        <v>6576</v>
+      </c>
+      <c r="W58" s="4">
+        <v>0</v>
+      </c>
       <c r="X58" s="1"/>
       <c r="Y58" s="4"/>
       <c r="Z58" s="4">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>6576</v>
       </c>
       <c r="AA58" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="38.25">
-      <c r="A59" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C59" s="1"/>
-      <c r="D59" s="4">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E59" s="4"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="I59" s="4">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="4">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K59" s="4"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O59" s="4">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="P59" s="4">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q59" s="4"/>
-      <c r="R59" s="1"/>
-      <c r="S59" s="4"/>
-      <c r="T59" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U59" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V59" s="4">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W59" s="4"/>
-      <c r="X59" s="1"/>
-      <c r="Y59" s="4"/>
-      <c r="Z59" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AA59" s="4">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:27" ht="15">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="5"/>
-      <c r="M60" s="5"/>
-      <c r="N60" s="5"/>
-      <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
-      <c r="Q60" s="5"/>
-      <c r="R60" s="5"/>
-      <c r="S60" s="5"/>
-      <c r="T60" s="5"/>
-      <c r="U60" s="5"/>
-      <c r="V60" s="5"/>
-      <c r="W60" s="5"/>
-      <c r="X60" s="5"/>
-      <c r="Y60" s="5"/>
-      <c r="Z60" s="5"/>
-      <c r="AA60" s="5"/>
-    </row>
-    <row r="61" spans="1:27" ht="15">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="5"/>
-      <c r="M61" s="5"/>
-      <c r="N61" s="5"/>
-      <c r="O61" s="5"/>
-      <c r="P61" s="5"/>
-      <c r="Q61" s="5"/>
-      <c r="R61" s="5"/>
-      <c r="S61" s="5"/>
-      <c r="T61" s="5"/>
-      <c r="U61" s="5"/>
-      <c r="V61" s="5"/>
-      <c r="W61" s="5"/>
-      <c r="X61" s="5"/>
-      <c r="Y61" s="5"/>
-      <c r="Z61" s="5"/>
-      <c r="AA61" s="5"/>
-    </row>
-    <row r="62" spans="1:27" ht="15">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="5"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="5"/>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="5"/>
-      <c r="R62" s="5"/>
-      <c r="S62" s="5"/>
-      <c r="T62" s="5"/>
-      <c r="U62" s="5"/>
-      <c r="V62" s="5"/>
-      <c r="W62" s="5"/>
-      <c r="X62" s="5"/>
-      <c r="Y62" s="5"/>
-      <c r="Z62" s="5"/>
-      <c r="AA62" s="5"/>
-    </row>
-    <row r="63" spans="1:27" ht="15">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="5"/>
-      <c r="O63" s="5"/>
-      <c r="P63" s="5"/>
-      <c r="Q63" s="5"/>
-      <c r="R63" s="5"/>
-      <c r="S63" s="5"/>
-      <c r="T63" s="5"/>
-      <c r="U63" s="5"/>
-      <c r="V63" s="5"/>
-      <c r="W63" s="5"/>
-      <c r="X63" s="5"/>
-      <c r="Y63" s="5"/>
-      <c r="Z63" s="5"/>
-      <c r="AA63" s="5"/>
-    </row>
-    <row r="64" spans="1:27" ht="15">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
-      <c r="K64" s="5"/>
-      <c r="L64" s="5"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="5"/>
-      <c r="O64" s="5"/>
-      <c r="P64" s="5"/>
-      <c r="Q64" s="5"/>
-      <c r="R64" s="5"/>
-      <c r="S64" s="5"/>
-      <c r="T64" s="5"/>
-      <c r="U64" s="5"/>
-      <c r="V64" s="5"/>
-      <c r="W64" s="5"/>
-      <c r="X64" s="5"/>
-      <c r="Y64" s="5"/>
-      <c r="Z64" s="5"/>
-      <c r="AA64" s="5"/>
-    </row>
-    <row r="65" spans="1:27" ht="15">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
-      <c r="K65" s="5"/>
-      <c r="L65" s="5"/>
-      <c r="M65" s="5"/>
-      <c r="N65" s="5"/>
-      <c r="O65" s="5"/>
-      <c r="P65" s="5"/>
-      <c r="Q65" s="5"/>
-      <c r="R65" s="5"/>
-      <c r="S65" s="5"/>
-      <c r="T65" s="5"/>
-      <c r="U65" s="5"/>
-      <c r="V65" s="5"/>
-      <c r="W65" s="5"/>
-      <c r="X65" s="5"/>
-      <c r="Y65" s="5"/>
-      <c r="Z65" s="5"/>
-      <c r="AA65" s="5"/>
-    </row>
-    <row r="66" spans="1:27" s="5" customFormat="1" ht="15"/>
-    <row r="67" spans="1:27" ht="15">
-      <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="5"/>
-      <c r="K67" s="5"/>
-      <c r="L67" s="5"/>
-      <c r="M67" s="5"/>
-      <c r="N67" s="5"/>
-      <c r="O67" s="5"/>
-      <c r="P67" s="5"/>
-      <c r="Q67" s="5"/>
-      <c r="R67" s="5"/>
-      <c r="S67" s="5"/>
-      <c r="T67" s="5"/>
-      <c r="U67" s="5"/>
-      <c r="V67" s="5"/>
-      <c r="W67" s="5"/>
-      <c r="X67" s="5"/>
-      <c r="Y67" s="5"/>
-      <c r="Z67" s="5"/>
-      <c r="AA67" s="5"/>
-    </row>
-    <row r="68" spans="1:27" ht="15">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="5"/>
-      <c r="K68" s="5"/>
-      <c r="L68" s="5"/>
-      <c r="M68" s="5"/>
-      <c r="N68" s="5"/>
-      <c r="O68" s="5"/>
-      <c r="P68" s="5"/>
-      <c r="Q68" s="5"/>
-      <c r="R68" s="5"/>
-      <c r="S68" s="5"/>
-      <c r="T68" s="5"/>
-      <c r="U68" s="5"/>
-      <c r="V68" s="5"/>
-      <c r="W68" s="5"/>
-      <c r="X68" s="5"/>
-      <c r="Y68" s="5"/>
-      <c r="Z68" s="5"/>
-      <c r="AA68" s="5"/>
-    </row>
-    <row r="69" spans="1:27" ht="15">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="5"/>
-      <c r="K69" s="5"/>
-      <c r="L69" s="5"/>
-      <c r="M69" s="5"/>
-      <c r="N69" s="5"/>
-      <c r="O69" s="5"/>
-      <c r="P69" s="5"/>
-      <c r="Q69" s="5"/>
-      <c r="R69" s="5"/>
-      <c r="S69" s="5"/>
-      <c r="T69" s="5"/>
-      <c r="U69" s="5"/>
-      <c r="V69" s="5"/>
-      <c r="W69" s="5"/>
-      <c r="X69" s="5"/>
-      <c r="Y69" s="5"/>
-      <c r="Z69" s="5"/>
-      <c r="AA69" s="5"/>
-    </row>
-    <row r="70" spans="1:27" ht="15">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5"/>
-      <c r="L70" s="5"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="5"/>
-      <c r="O70" s="5"/>
-      <c r="P70" s="5"/>
-      <c r="Q70" s="5"/>
-      <c r="R70" s="5"/>
-      <c r="S70" s="5"/>
-      <c r="T70" s="5"/>
-      <c r="U70" s="5"/>
-      <c r="V70" s="5"/>
-      <c r="W70" s="5"/>
-      <c r="X70" s="5"/>
-      <c r="Y70" s="5"/>
-      <c r="Z70" s="5"/>
-      <c r="AA70" s="5"/>
-    </row>
-    <row r="71" spans="1:27" ht="15">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="5"/>
-      <c r="K71" s="5"/>
-      <c r="L71" s="5"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="5"/>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="5"/>
-      <c r="R71" s="5"/>
-      <c r="S71" s="5"/>
-      <c r="T71" s="5"/>
-      <c r="U71" s="5"/>
-      <c r="V71" s="5"/>
-      <c r="W71" s="5"/>
-      <c r="X71" s="5"/>
-      <c r="Y71" s="5"/>
-      <c r="Z71" s="5"/>
-      <c r="AA71" s="5"/>
-    </row>
-    <row r="72" spans="1:27" ht="15">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="5"/>
-      <c r="M72" s="5"/>
-      <c r="N72" s="5"/>
-      <c r="O72" s="5"/>
-      <c r="P72" s="5"/>
-      <c r="Q72" s="5"/>
-      <c r="R72" s="5"/>
-      <c r="S72" s="5"/>
-      <c r="T72" s="5"/>
-      <c r="U72" s="5"/>
-      <c r="V72" s="5"/>
-      <c r="W72" s="5"/>
-      <c r="X72" s="5"/>
-      <c r="Y72" s="5"/>
-      <c r="Z72" s="5"/>
-      <c r="AA72" s="5"/>
-    </row>
-    <row r="73" spans="1:27" ht="15">
-      <c r="A73" s="5"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
-      <c r="I73" s="5"/>
-      <c r="J73" s="5"/>
-      <c r="K73" s="5"/>
-      <c r="L73" s="5"/>
-      <c r="M73" s="5"/>
-      <c r="N73" s="5"/>
-      <c r="O73" s="5"/>
-      <c r="P73" s="5"/>
-      <c r="Q73" s="5"/>
-      <c r="R73" s="5"/>
-      <c r="S73" s="5"/>
-      <c r="T73" s="5"/>
-      <c r="U73" s="5"/>
-      <c r="V73" s="5"/>
-      <c r="W73" s="5"/>
-      <c r="X73" s="5"/>
-      <c r="Y73" s="5"/>
-      <c r="Z73" s="5"/>
-      <c r="AA73" s="5"/>
-    </row>
-    <row r="74" spans="1:27" ht="15">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
-      <c r="N74" s="5"/>
-      <c r="O74" s="5"/>
-      <c r="P74" s="5"/>
-      <c r="Q74" s="5"/>
-      <c r="R74" s="5"/>
-      <c r="S74" s="5"/>
-      <c r="T74" s="5"/>
-      <c r="U74" s="5"/>
-      <c r="V74" s="5"/>
-      <c r="W74" s="5"/>
-      <c r="X74" s="5"/>
-      <c r="Y74" s="5"/>
-      <c r="Z74" s="5"/>
-      <c r="AA74" s="5"/>
-    </row>
-    <row r="75" spans="1:27" ht="15">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-      <c r="I75" s="5"/>
-      <c r="J75" s="5"/>
-      <c r="K75" s="5"/>
-      <c r="L75" s="5"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="5"/>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="5"/>
-      <c r="R75" s="5"/>
-      <c r="S75" s="5"/>
-      <c r="T75" s="5"/>
-      <c r="U75" s="5"/>
-      <c r="V75" s="5"/>
-      <c r="W75" s="5"/>
-      <c r="X75" s="5"/>
-      <c r="Y75" s="5"/>
-      <c r="Z75" s="5"/>
-      <c r="AA75" s="5"/>
-    </row>
-    <row r="76" spans="1:27" ht="15">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-      <c r="I76" s="5"/>
-      <c r="J76" s="5"/>
-      <c r="K76" s="5"/>
-      <c r="L76" s="5"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="5"/>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="5"/>
-      <c r="R76" s="5"/>
-      <c r="S76" s="5"/>
-      <c r="T76" s="5"/>
-      <c r="U76" s="5"/>
-      <c r="V76" s="5"/>
-      <c r="W76" s="5"/>
-      <c r="X76" s="5"/>
-      <c r="Y76" s="5"/>
-      <c r="Z76" s="5"/>
-      <c r="AA76" s="5"/>
-    </row>
-    <row r="77" spans="1:27" ht="15">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
-      <c r="I77" s="5"/>
-      <c r="J77" s="5"/>
-      <c r="K77" s="5"/>
-      <c r="L77" s="5"/>
-      <c r="M77" s="5"/>
-      <c r="N77" s="5"/>
-      <c r="O77" s="5"/>
-      <c r="P77" s="5"/>
-      <c r="Q77" s="5"/>
-      <c r="R77" s="5"/>
-      <c r="S77" s="5"/>
-      <c r="T77" s="5"/>
-      <c r="U77" s="5"/>
-      <c r="V77" s="5"/>
-      <c r="W77" s="5"/>
-      <c r="X77" s="5"/>
-      <c r="Y77" s="5"/>
-      <c r="Z77" s="5"/>
-      <c r="AA77" s="5"/>
-    </row>
-    <row r="78" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A78"/>
-      <c r="B78"/>
-      <c r="C78"/>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
-      <c r="G78"/>
-      <c r="H78"/>
-      <c r="I78"/>
-      <c r="J78"/>
-      <c r="K78"/>
-      <c r="L78"/>
-      <c r="M78"/>
-      <c r="N78"/>
-      <c r="O78"/>
-      <c r="P78"/>
-      <c r="Q78"/>
-      <c r="R78"/>
-      <c r="S78"/>
-      <c r="T78"/>
-      <c r="U78"/>
-      <c r="V78"/>
-      <c r="W78"/>
-      <c r="X78"/>
-      <c r="Y78"/>
-      <c r="Z78"/>
-      <c r="AA78"/>
-    </row>
+    <row r="59" spans="1:27" ht="15"/>
+    <row r="60" spans="1:27" ht="15"/>
+    <row r="61" spans="1:27" ht="15"/>
+    <row r="62" spans="1:27" ht="15"/>
+    <row r="63" spans="1:27" ht="15"/>
+    <row r="64" spans="1:27" ht="15"/>
+    <row r="65" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A65"/>
+      <c r="B65"/>
+      <c r="C65"/>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65"/>
+      <c r="G65"/>
+      <c r="H65"/>
+      <c r="I65"/>
+      <c r="J65"/>
+      <c r="K65"/>
+      <c r="L65"/>
+      <c r="M65"/>
+      <c r="N65"/>
+      <c r="O65"/>
+      <c r="P65"/>
+      <c r="Q65"/>
+      <c r="R65"/>
+      <c r="S65"/>
+      <c r="T65"/>
+      <c r="U65"/>
+      <c r="V65"/>
+      <c r="W65"/>
+      <c r="X65"/>
+      <c r="Y65"/>
+      <c r="Z65"/>
+      <c r="AA65"/>
+    </row>
+    <row r="66" spans="1:27" ht="15"/>
+    <row r="67" spans="1:27" ht="15"/>
+    <row r="68" spans="1:27" ht="15"/>
+    <row r="69" spans="1:27" ht="15"/>
+    <row r="70" spans="1:27" ht="15"/>
+    <row r="71" spans="1:27" ht="15"/>
+    <row r="72" spans="1:27" ht="15"/>
+    <row r="73" spans="1:27" ht="15"/>
+    <row r="74" spans="1:27" ht="15"/>
+    <row r="75" spans="1:27" ht="15"/>
+    <row r="76" spans="1:27" ht="15"/>
+    <row r="77" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A77"/>
+      <c r="B77"/>
+      <c r="C77"/>
+      <c r="D77"/>
+      <c r="E77"/>
+      <c r="F77"/>
+      <c r="G77"/>
+      <c r="H77"/>
+      <c r="I77"/>
+      <c r="J77"/>
+      <c r="K77"/>
+      <c r="L77"/>
+      <c r="M77"/>
+      <c r="N77"/>
+      <c r="O77"/>
+      <c r="P77"/>
+      <c r="Q77"/>
+      <c r="R77"/>
+      <c r="S77"/>
+      <c r="T77"/>
+      <c r="U77"/>
+      <c r="V77"/>
+      <c r="W77"/>
+      <c r="X77"/>
+      <c r="Y77"/>
+      <c r="Z77"/>
+      <c r="AA77"/>
+    </row>
+    <row r="78" spans="1:27" ht="15"/>
     <row r="79" spans="1:27" ht="15"/>
     <row r="80" spans="1:27" ht="15"/>
     <row r="81" spans="1:27" ht="15"/>
@@ -14651,36 +13346,36 @@
     <row r="86" spans="1:27" ht="15"/>
     <row r="87" spans="1:27" ht="15"/>
     <row r="88" spans="1:27" ht="15"/>
-    <row r="89" spans="1:27" ht="15"/>
-    <row r="90" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A90"/>
-      <c r="B90"/>
-      <c r="C90"/>
-      <c r="D90"/>
-      <c r="E90"/>
-      <c r="F90"/>
-      <c r="G90"/>
-      <c r="H90"/>
-      <c r="I90"/>
-      <c r="J90"/>
-      <c r="K90"/>
-      <c r="L90"/>
-      <c r="M90"/>
-      <c r="N90"/>
-      <c r="O90"/>
-      <c r="P90"/>
-      <c r="Q90"/>
-      <c r="R90"/>
-      <c r="S90"/>
-      <c r="T90"/>
-      <c r="U90"/>
-      <c r="V90"/>
-      <c r="W90"/>
-      <c r="X90"/>
-      <c r="Y90"/>
-      <c r="Z90"/>
-      <c r="AA90"/>
-    </row>
+    <row r="89" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A89"/>
+      <c r="B89"/>
+      <c r="C89"/>
+      <c r="D89"/>
+      <c r="E89"/>
+      <c r="F89"/>
+      <c r="G89"/>
+      <c r="H89"/>
+      <c r="I89"/>
+      <c r="J89"/>
+      <c r="K89"/>
+      <c r="L89"/>
+      <c r="M89"/>
+      <c r="N89"/>
+      <c r="O89"/>
+      <c r="P89"/>
+      <c r="Q89"/>
+      <c r="R89"/>
+      <c r="S89"/>
+      <c r="T89"/>
+      <c r="U89"/>
+      <c r="V89"/>
+      <c r="W89"/>
+      <c r="X89"/>
+      <c r="Y89"/>
+      <c r="Z89"/>
+      <c r="AA89"/>
+    </row>
+    <row r="90" spans="1:27" ht="15"/>
     <row r="91" spans="1:27" ht="15"/>
     <row r="92" spans="1:27" ht="15"/>
     <row r="93" spans="1:27" ht="15"/>
@@ -14691,36 +13386,36 @@
     <row r="98" spans="1:27" ht="15"/>
     <row r="99" spans="1:27" ht="15"/>
     <row r="100" spans="1:27" ht="15"/>
-    <row r="101" spans="1:27" ht="15"/>
-    <row r="102" spans="1:27" s="5" customFormat="1" ht="15">
-      <c r="A102"/>
-      <c r="B102"/>
-      <c r="C102"/>
-      <c r="D102"/>
-      <c r="E102"/>
-      <c r="F102"/>
-      <c r="G102"/>
-      <c r="H102"/>
-      <c r="I102"/>
-      <c r="J102"/>
-      <c r="K102"/>
-      <c r="L102"/>
-      <c r="M102"/>
-      <c r="N102"/>
-      <c r="O102"/>
-      <c r="P102"/>
-      <c r="Q102"/>
-      <c r="R102"/>
-      <c r="S102"/>
-      <c r="T102"/>
-      <c r="U102"/>
-      <c r="V102"/>
-      <c r="W102"/>
-      <c r="X102"/>
-      <c r="Y102"/>
-      <c r="Z102"/>
-      <c r="AA102"/>
-    </row>
+    <row r="101" spans="1:27" s="5" customFormat="1" ht="15">
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101"/>
+      <c r="I101"/>
+      <c r="J101"/>
+      <c r="K101"/>
+      <c r="L101"/>
+      <c r="M101"/>
+      <c r="N101"/>
+      <c r="O101"/>
+      <c r="P101"/>
+      <c r="Q101"/>
+      <c r="R101"/>
+      <c r="S101"/>
+      <c r="T101"/>
+      <c r="U101"/>
+      <c r="V101"/>
+      <c r="W101"/>
+      <c r="X101"/>
+      <c r="Y101"/>
+      <c r="Z101"/>
+      <c r="AA101"/>
+    </row>
+    <row r="102" spans="1:27" ht="15"/>
     <row r="103" spans="1:27" ht="15"/>
     <row r="104" spans="1:27" ht="15"/>
     <row r="105" spans="1:27" ht="15"/>
@@ -14731,36 +13426,36 @@
     <row r="110" spans="1:27" ht="15"/>
     <row r="111" spans="1:27" ht="15"/>
     <row r="112" spans="1:27" ht="15"/>
-    <row r="113" spans="1:28" ht="15"/>
-    <row r="114" spans="1:28" s="5" customFormat="1">
-      <c r="A114"/>
-      <c r="B114"/>
-      <c r="C114"/>
-      <c r="D114"/>
-      <c r="E114"/>
-      <c r="F114"/>
-      <c r="G114"/>
-      <c r="H114"/>
-      <c r="I114"/>
-      <c r="J114"/>
-      <c r="K114"/>
-      <c r="L114"/>
-      <c r="M114"/>
-      <c r="N114"/>
-      <c r="O114"/>
-      <c r="P114"/>
-      <c r="Q114"/>
-      <c r="R114"/>
-      <c r="S114"/>
-      <c r="T114"/>
-      <c r="U114"/>
-      <c r="V114"/>
-      <c r="W114"/>
-      <c r="X114"/>
-      <c r="Y114"/>
-      <c r="Z114"/>
-      <c r="AA114"/>
-    </row>
+    <row r="113" spans="1:28" s="5" customFormat="1" ht="15">
+      <c r="A113"/>
+      <c r="B113"/>
+      <c r="C113"/>
+      <c r="D113"/>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113"/>
+      <c r="H113"/>
+      <c r="I113"/>
+      <c r="J113"/>
+      <c r="K113"/>
+      <c r="L113"/>
+      <c r="M113"/>
+      <c r="N113"/>
+      <c r="O113"/>
+      <c r="P113"/>
+      <c r="Q113"/>
+      <c r="R113"/>
+      <c r="S113"/>
+      <c r="T113"/>
+      <c r="U113"/>
+      <c r="V113"/>
+      <c r="W113"/>
+      <c r="X113"/>
+      <c r="Y113"/>
+      <c r="Z113"/>
+      <c r="AA113"/>
+    </row>
+    <row r="114" spans="1:28" ht="15"/>
     <row r="115" spans="1:28" ht="15"/>
     <row r="116" spans="1:28" ht="15"/>
     <row r="117" spans="1:28" ht="15"/>
@@ -14768,35 +13463,37 @@
     <row r="119" spans="1:28" ht="15"/>
     <row r="120" spans="1:28" ht="15"/>
     <row r="121" spans="1:28" ht="15"/>
-    <row r="122" spans="1:28" ht="15"/>
-    <row r="123" spans="1:28" s="5" customFormat="1">
-      <c r="A123"/>
-      <c r="B123"/>
-      <c r="C123"/>
-      <c r="D123"/>
-      <c r="E123"/>
-      <c r="F123"/>
-      <c r="G123"/>
-      <c r="H123"/>
-      <c r="I123"/>
-      <c r="J123"/>
-      <c r="K123"/>
-      <c r="L123"/>
-      <c r="M123"/>
-      <c r="N123"/>
-      <c r="O123"/>
-      <c r="P123"/>
-      <c r="Q123"/>
-      <c r="R123"/>
-      <c r="S123"/>
-      <c r="T123"/>
-      <c r="U123"/>
-      <c r="V123"/>
-      <c r="W123"/>
-      <c r="X123"/>
-      <c r="Y123"/>
-      <c r="Z123"/>
-      <c r="AA123"/>
+    <row r="122" spans="1:28" s="5" customFormat="1" ht="15">
+      <c r="A122"/>
+      <c r="B122"/>
+      <c r="C122"/>
+      <c r="D122"/>
+      <c r="E122"/>
+      <c r="F122"/>
+      <c r="G122"/>
+      <c r="H122"/>
+      <c r="I122"/>
+      <c r="J122"/>
+      <c r="K122"/>
+      <c r="L122"/>
+      <c r="M122"/>
+      <c r="N122"/>
+      <c r="O122"/>
+      <c r="P122"/>
+      <c r="Q122"/>
+      <c r="R122"/>
+      <c r="S122"/>
+      <c r="T122"/>
+      <c r="U122"/>
+      <c r="V122"/>
+      <c r="W122"/>
+      <c r="X122"/>
+      <c r="Y122"/>
+      <c r="Z122"/>
+      <c r="AA122"/>
+    </row>
+    <row r="123" spans="1:28">
+      <c r="AB123" s="5"/>
     </row>
     <row r="124" spans="1:28">
       <c r="AB124" s="5"/>
@@ -14846,18 +13543,16 @@
     <row r="139" spans="28:28">
       <c r="AB139" s="5"/>
     </row>
-    <row r="140" spans="28:28">
-      <c r="AB140" s="5"/>
-    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C52:C59 C2" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 H52:L59 P2:R2 D52:F59 V2:X2 Z4:AA14 Z16:AA26 Z28:AA38 Z40:AA50 N52:R59 T52:X59 Z52:AA59 D2:F2 D4:F14 D16:F26 D28:F38 H28:L38 N28:R38 D40:F50 H4:L14 H16:L26 H40:L50 N4:R14 N16:R26 T4:X14 T16:X26 N40:R50 T28:X38 T40:X50" name="LAS"/>
-    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 Y52:Y59 G52:G59 M52:M59 S52:S59 Y4:Y14 G4:G14 M4:M14 S4:S14 Y16:Y26 G16:G26 M16:M26 S16:S26 G28:G38 G40:G50 M40:M50 M28:M38 S28:S38 S40:S50 Y28:Y38 Y40:Y50" name="SOURCE"/>
-    <protectedRange sqref="C4:C14" name="Textbooks_1"/>
-    <protectedRange sqref="C16:C26" name="Textbooks_2"/>
-    <protectedRange sqref="C28:C38" name="Textbooks_3"/>
-    <protectedRange sqref="C40:C50" name="Textbooks_4"/>
+    <protectedRange sqref="C2" name="Textbooks"/>
+    <protectedRange sqref="J2:L2 P2:R2 V2:X2 Z3:AA13 Z15:AA25 Z27:AA37 Z39:AA49 Z51:AA58 D2:F2 D3:F13 D15:F25 D27:F37 H27:L37 N27:R37 D39:F49 H3:L13 H15:L25 H39:L49 N3:R13 N15:R25 T3:X13 T15:X25 N39:R49 T27:X37 T39:X49 D51:F58 H51:L58 N51:R58 T51:X58" name="LAS"/>
+    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 Y51:Y58 G51:G58 M51:M58 S51:S58 Y3:Y13 G3:G13 M3:M13 S3:S13 Y15:Y25 G15:G25 M15:M25 S15:S25 G27:G37 G39:G49 M39:M49 M27:M37 S27:S37 S39:S49 Y27:Y37 Y39:Y49" name="SOURCE"/>
+    <protectedRange sqref="C3:C13" name="Textbooks_1"/>
+    <protectedRange sqref="C15:C25" name="Textbooks_2"/>
+    <protectedRange sqref="C27:C37" name="Textbooks_3"/>
+    <protectedRange sqref="C39:C49" name="Textbooks_4"/>
+    <protectedRange sqref="C51:C58" name="Textbooks_5"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -14867,10 +13562,10 @@
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S52:S59 Y52:Y59 G52:G59 M4:M14 G4:G14 Y4:Y14 S4:S14 S16:S26 M16:M26 G16:G26 Y16:Y26 S40:S50 M28:M38 M52:M59 G28:G38 G40:G50 Y28:Y38 S28:S38 M40:M50 Y40:Y50" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S51:S58 Y51:Y58 G51:G58 M3:M13 G3:G13 Y3:Y13 S3:S13 S15:S25 M15:M25 G15:G25 Y15:Y25 S39:S49 M27:M37 M51:M58 G27:G37 G39:G49 Y27:Y37 S27:S37 M39:M49 Y39:Y49" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X52:X59 F4:F14 F16:F26 F28:F38 F40:F50 F52:F59 L4:L14 L16:L26 L28:L38 L40:L50 L52:L59 R4:R14 R16:R26 R28:R38 X28:X38 R52:R59 X4:X14 X16:X26 R40:R50 X40:X50" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X51:X58 F3:F13 F15:F25 F27:F37 F39:F49 F51:F58 L3:L13 L15:L25 L27:L37 L39:L49 L51:L58 R3:R13 R15:R25 R27:R37 X27:X37 R51:R58 X3:X13 X15:X25 R39:R49 X39:X49" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
